--- a/Financial Analysis/ITX.xlsx
+++ b/Financial Analysis/ITX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3944CEC-1FDF-4BD8-B3F8-17B1EFBDC1AF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD726E2A-39E3-4D14-B794-8EB43BDA516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{8E1A3549-F8B8-4E5D-8D16-11995B547C13}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="78">
   <si>
     <t>ITX</t>
   </si>
@@ -209,6 +209,57 @@
   </si>
   <si>
     <t>Slightly overvalued</t>
+  </si>
+  <si>
+    <t>Q122</t>
+  </si>
+  <si>
+    <t>Q222</t>
+  </si>
+  <si>
+    <t>Q322</t>
+  </si>
+  <si>
+    <t>Q422</t>
+  </si>
+  <si>
+    <t>Q123</t>
+  </si>
+  <si>
+    <t>Q223</t>
+  </si>
+  <si>
+    <t>Q323</t>
+  </si>
+  <si>
+    <t>Q423</t>
+  </si>
+  <si>
+    <t>Q124</t>
+  </si>
+  <si>
+    <t>Q224</t>
+  </si>
+  <si>
+    <t>Q324</t>
+  </si>
+  <si>
+    <t>Q424</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
   </si>
 </sst>
 </file>
@@ -269,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -284,12 +335,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,14 +411,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -385,7 +435,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23180040" y="0"/>
+          <a:off x="38221920" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -735,17 +785,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>31.81</v>
+        <v>46.89</v>
       </c>
       <c r="E3" s="3">
-        <v>44336</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>44336</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="3">
-        <v>44356</v>
+        <v>45994</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -753,10 +803,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>3114.9</v>
+        <f>3115.8</f>
+        <v>3115.8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -765,7 +816,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>99084.968999999997</v>
+        <v>146099.86200000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -773,11 +824,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>7398+176+261</f>
-        <v>7835</v>
+        <f>5139+4874</f>
+        <v>10013</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,11 +836,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>11+3</f>
-        <v>14</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -798,7 +849,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>7821</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -807,7 +858,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>91263.968999999997</v>
+        <v>136087.86200000002</v>
       </c>
     </row>
   </sheetData>
@@ -818,90 +869,200 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96837BB2-D8B4-42AE-9AC6-EEBF01A19113}">
-  <dimension ref="B1:EM27"/>
+  <dimension ref="B1:FH40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="26" width="10.5546875" customWidth="1"/>
-    <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="42" width="10.5546875" customWidth="1"/>
+    <col min="44" max="58" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="63" width="10.5546875" customWidth="1"/>
+    <col min="65" max="65" width="12" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:143" x14ac:dyDescent="0.3">
-      <c r="C1" s="13">
+    <row r="1" spans="2:164" x14ac:dyDescent="0.3">
+      <c r="C1" s="11">
         <v>42490</v>
       </c>
-      <c r="D1" s="13">
+      <c r="D1" s="11">
         <v>42582</v>
       </c>
-      <c r="E1" s="13">
+      <c r="E1" s="11">
         <v>42674</v>
       </c>
-      <c r="F1" s="13">
+      <c r="F1" s="11">
         <v>42766</v>
       </c>
-      <c r="G1" s="13">
+      <c r="G1" s="11">
         <v>42855</v>
       </c>
-      <c r="H1" s="13">
+      <c r="H1" s="11">
         <v>42947</v>
       </c>
-      <c r="I1" s="13">
+      <c r="I1" s="11">
         <v>43039</v>
       </c>
-      <c r="J1" s="13">
+      <c r="J1" s="11">
         <v>43131</v>
       </c>
-      <c r="K1" s="13">
+      <c r="K1" s="11">
         <v>43220</v>
       </c>
-      <c r="L1" s="13">
+      <c r="L1" s="11">
         <v>43312</v>
       </c>
-      <c r="M1" s="13">
+      <c r="M1" s="11">
         <v>43404</v>
       </c>
-      <c r="N1" s="13">
+      <c r="N1" s="11">
         <v>43496</v>
       </c>
-      <c r="O1" s="13">
+      <c r="O1" s="11">
         <v>43585</v>
       </c>
-      <c r="P1" s="13">
+      <c r="P1" s="11">
         <v>43677</v>
       </c>
-      <c r="Q1" s="13">
+      <c r="Q1" s="11">
         <v>43769</v>
       </c>
-      <c r="R1" s="13">
+      <c r="R1" s="11">
         <v>43861</v>
       </c>
-      <c r="S1" s="13">
+      <c r="S1" s="11">
         <v>43951</v>
       </c>
-      <c r="T1" s="13">
+      <c r="T1" s="11">
         <v>44043</v>
       </c>
-      <c r="U1" s="13">
+      <c r="U1" s="11">
         <v>44135</v>
       </c>
-      <c r="V1" s="13">
+      <c r="V1" s="11">
         <v>44227</v>
       </c>
-      <c r="W1" s="13">
+      <c r="W1" s="11">
         <v>44316</v>
       </c>
-      <c r="X1" s="13">
+      <c r="X1" s="11">
         <v>44408</v>
       </c>
-      <c r="Y1" s="13">
+      <c r="Y1" s="11">
         <v>44500</v>
       </c>
-      <c r="Z1" s="13">
+      <c r="Z1" s="11">
         <v>44592</v>
       </c>
+      <c r="AA1" s="11">
+        <v>44681</v>
+      </c>
+      <c r="AB1" s="11">
+        <v>44773</v>
+      </c>
+      <c r="AC1" s="11">
+        <v>44865</v>
+      </c>
+      <c r="AD1" s="11">
+        <v>44957</v>
+      </c>
+      <c r="AE1" s="11">
+        <v>45046</v>
+      </c>
+      <c r="AF1" s="11">
+        <v>45138</v>
+      </c>
+      <c r="AG1" s="11">
+        <v>45230</v>
+      </c>
+      <c r="AH1" s="11">
+        <v>45322</v>
+      </c>
+      <c r="AI1" s="11">
+        <v>45412</v>
+      </c>
+      <c r="AJ1" s="11">
+        <v>45504</v>
+      </c>
+      <c r="AK1" s="11">
+        <v>45596</v>
+      </c>
+      <c r="AL1" s="11">
+        <v>45688</v>
+      </c>
+      <c r="AM1" s="11">
+        <v>45777</v>
+      </c>
+      <c r="AN1" s="11">
+        <v>45869</v>
+      </c>
+      <c r="AO1" s="11">
+        <v>45961</v>
+      </c>
+      <c r="AP1" s="11">
+        <v>46053</v>
+      </c>
+      <c r="AR1" s="11">
+        <v>42766</v>
+      </c>
+      <c r="AS1" s="11">
+        <v>43131</v>
+      </c>
+      <c r="AT1" s="11">
+        <v>43496</v>
+      </c>
+      <c r="AU1" s="11">
+        <v>43861</v>
+      </c>
+      <c r="AV1" s="11">
+        <v>44227</v>
+      </c>
+      <c r="AW1" s="11">
+        <v>44592</v>
+      </c>
+      <c r="AX1" s="11">
+        <v>44957</v>
+      </c>
+      <c r="AY1" s="11">
+        <v>45322</v>
+      </c>
+      <c r="AZ1" s="11">
+        <v>45688</v>
+      </c>
+      <c r="BA1" s="11">
+        <v>46053</v>
+      </c>
+      <c r="BB1" s="11">
+        <v>46418</v>
+      </c>
+      <c r="BC1" s="11">
+        <v>46783</v>
+      </c>
+      <c r="BD1" s="11">
+        <v>47149</v>
+      </c>
+      <c r="BE1" s="11">
+        <v>47514</v>
+      </c>
+      <c r="BF1" s="11">
+        <v>47879</v>
+      </c>
+      <c r="BG1" s="11">
+        <v>48244</v>
+      </c>
+      <c r="BH1" s="11">
+        <v>48610</v>
+      </c>
+      <c r="BI1" s="11">
+        <v>48975</v>
+      </c>
+      <c r="BJ1" s="11">
+        <v>49340</v>
+      </c>
+      <c r="BK1" s="11">
+        <v>49705</v>
+      </c>
     </row>
-    <row r="2" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:164" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
@@ -974,196 +1135,301 @@
       <c r="Z2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AB2">
+      <c r="AA2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR2">
         <v>2016</v>
       </c>
-      <c r="AC2">
+      <c r="AS2">
         <v>2017</v>
       </c>
-      <c r="AD2">
+      <c r="AT2">
         <v>2018</v>
       </c>
-      <c r="AE2">
+      <c r="AU2">
         <v>2019</v>
       </c>
-      <c r="AF2">
+      <c r="AV2">
         <v>2020</v>
       </c>
-      <c r="AG2">
+      <c r="AW2">
         <v>2021</v>
       </c>
-      <c r="AH2">
+      <c r="AX2">
         <v>2022</v>
       </c>
-      <c r="AI2">
+      <c r="AY2">
         <v>2023</v>
       </c>
-      <c r="AJ2">
+      <c r="AZ2">
         <v>2024</v>
       </c>
-      <c r="AK2">
+      <c r="BA2">
         <v>2025</v>
       </c>
-      <c r="AL2">
+      <c r="BB2">
         <v>2026</v>
       </c>
-      <c r="AM2">
+      <c r="BC2">
         <v>2027</v>
       </c>
-      <c r="AN2">
+      <c r="BD2">
         <v>2028</v>
       </c>
-      <c r="AO2">
+      <c r="BE2">
         <v>2029</v>
       </c>
-      <c r="AP2">
+      <c r="BF2">
         <v>2030</v>
       </c>
+      <c r="BG2">
+        <v>2031</v>
+      </c>
+      <c r="BH2">
+        <v>2032</v>
+      </c>
+      <c r="BI2">
+        <v>2033</v>
+      </c>
+      <c r="BJ2">
+        <v>2034</v>
+      </c>
+      <c r="BK2">
+        <v>2035</v>
+      </c>
     </row>
-    <row r="3" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:164" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>4879</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>5586</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>5937</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>6908</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>5569</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>6102</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>6291</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>7373</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>5654</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>6372</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>6412</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>7708</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>5927</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="9">
         <v>6893</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="9">
         <v>7000</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="9">
         <v>8466</v>
       </c>
-      <c r="S3" s="10">
+      <c r="S3" s="9">
         <v>3303</v>
       </c>
-      <c r="T3" s="10">
+      <c r="T3" s="9">
         <f>8033-S3</f>
         <v>4730</v>
       </c>
-      <c r="U3" s="10">
+      <c r="U3" s="9">
         <f>14085-T3-S3</f>
         <v>6052</v>
       </c>
-      <c r="V3" s="10">
-        <f>AF3-U3-T3-S3</f>
+      <c r="V3" s="9">
+        <f>AV3-U3-T3-S3</f>
         <v>6317</v>
       </c>
-      <c r="W3" s="10">
+      <c r="W3" s="9">
         <f>S3*1.55</f>
         <v>5119.6500000000005</v>
       </c>
-      <c r="X3" s="10">
+      <c r="X3" s="9">
         <f>T3*1.3</f>
         <v>6149</v>
       </c>
-      <c r="Y3" s="10">
+      <c r="Y3" s="9">
         <f>U3*1.1</f>
         <v>6657.2000000000007</v>
       </c>
-      <c r="Z3" s="10">
+      <c r="Z3" s="9">
         <f>V3*1.12</f>
         <v>7075.0400000000009</v>
       </c>
-      <c r="AB3" s="10">
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9">
+        <v>8150</v>
+      </c>
+      <c r="AJ3" s="9">
+        <f>AJ28-AI3</f>
+        <v>9915</v>
+      </c>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9">
+        <v>8274</v>
+      </c>
+      <c r="AN3" s="9">
+        <f>AN28-AM3</f>
+        <v>10083</v>
+      </c>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AR3" s="9">
         <f>SUM(C3:F3)</f>
         <v>23310</v>
       </c>
-      <c r="AC3" s="10">
+      <c r="AS3" s="9">
         <f>SUM(G3:J3)</f>
         <v>25335</v>
       </c>
-      <c r="AD3" s="10">
+      <c r="AT3" s="9">
         <f>SUM(K3:N3)</f>
         <v>26146</v>
       </c>
-      <c r="AE3" s="10">
+      <c r="AU3" s="9">
         <f>SUM(O3:R3)</f>
         <v>28286</v>
       </c>
-      <c r="AF3" s="10">
+      <c r="AV3" s="9">
         <v>20402</v>
       </c>
-      <c r="AG3" s="10">
-        <f>SUM(W3:Z3)</f>
-        <v>25000.890000000003</v>
-      </c>
-      <c r="AH3" s="10">
-        <f>AG3*1.1</f>
-        <v>27500.979000000007</v>
-      </c>
-      <c r="AI3" s="10">
-        <f>AH3*1.08</f>
-        <v>29701.057320000011</v>
-      </c>
-      <c r="AJ3" s="10">
-        <f>AI3*1.05</f>
-        <v>31186.110186000013</v>
-      </c>
-      <c r="AK3" s="10">
-        <f>AJ3*1.05</f>
-        <v>32745.415695300013</v>
-      </c>
-      <c r="AL3" s="10">
-        <f>AK3*1.04</f>
-        <v>34055.232323112017</v>
-      </c>
-      <c r="AM3" s="10">
-        <f>AL3*1.03</f>
-        <v>35076.889292805376</v>
-      </c>
-      <c r="AN3" s="10">
-        <f>AM3*1.03</f>
-        <v>36129.195971589535</v>
-      </c>
-      <c r="AO3" s="10">
-        <f t="shared" ref="AO3:AP3" si="0">AN3*1.03</f>
-        <v>37213.071850737222</v>
-      </c>
-      <c r="AP3" s="10">
+      <c r="AW3" s="9">
+        <v>27716</v>
+      </c>
+      <c r="AX3" s="9">
+        <v>32569</v>
+      </c>
+      <c r="AY3" s="9">
+        <v>35947</v>
+      </c>
+      <c r="AZ3" s="9">
+        <v>38632</v>
+      </c>
+      <c r="BA3" s="9">
+        <f>AZ3*1.02</f>
+        <v>39404.639999999999</v>
+      </c>
+      <c r="BB3" s="9">
+        <f>BA3*1.02</f>
+        <v>40192.732799999998</v>
+      </c>
+      <c r="BC3" s="9">
+        <f>BB3*1.03</f>
+        <v>41398.514783999999</v>
+      </c>
+      <c r="BD3" s="9">
+        <f>BC3*1.03</f>
+        <v>42640.470227520003</v>
+      </c>
+      <c r="BE3" s="9">
+        <f t="shared" ref="BE3:BF3" si="0">BD3*1.03</f>
+        <v>43919.684334345606</v>
+      </c>
+      <c r="BF3" s="9">
         <f t="shared" si="0"/>
-        <v>38329.464006259339</v>
+        <v>45237.274864375977</v>
+      </c>
+      <c r="BG3" s="9">
+        <f>BF3*1.02</f>
+        <v>46142.020361663497</v>
+      </c>
+      <c r="BH3" s="9">
+        <f t="shared" ref="BH3:BK3" si="1">BG3*1.02</f>
+        <v>47064.860768896768</v>
+      </c>
+      <c r="BI3" s="9">
+        <f t="shared" si="1"/>
+        <v>48006.157984274701</v>
+      </c>
+      <c r="BJ3" s="9">
+        <f t="shared" si="1"/>
+        <v>48966.281143960194</v>
+      </c>
+      <c r="BK3" s="9">
+        <f t="shared" si="1"/>
+        <v>49945.606766839395</v>
       </c>
     </row>
-    <row r="4" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>13</v>
       </c>
@@ -1226,8 +1492,8 @@
         <f>5913-T4-S4</f>
         <v>2392</v>
       </c>
-      <c r="V4" s="11">
-        <f>AF4-U4-T4-S4</f>
+      <c r="V4" s="5">
+        <f>AV4-U4-T4-S4</f>
         <v>3100</v>
       </c>
       <c r="W4" s="5">
@@ -1235,239 +1501,329 @@
         <v>2099.0565000000006</v>
       </c>
       <c r="X4" s="5">
-        <f t="shared" ref="X4:Z4" si="1">X3-X5</f>
+        <f t="shared" ref="X4:Z4" si="2">X3-X5</f>
         <v>2767.0499999999997</v>
       </c>
       <c r="Y4" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2729.4520000000007</v>
       </c>
       <c r="Z4" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3325.2688000000003</v>
       </c>
-      <c r="AB4" s="11">
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5">
+        <v>3210</v>
+      </c>
+      <c r="AJ4" s="12">
+        <f>AJ29-AI4</f>
+        <v>4314</v>
+      </c>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5">
+        <v>3262</v>
+      </c>
+      <c r="AN4" s="12">
+        <f>AN29-AM4</f>
+        <v>4392</v>
+      </c>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AR4" s="5">
         <f>SUM(C4:F4)</f>
         <v>10032</v>
       </c>
-      <c r="AC4" s="11">
+      <c r="AS4" s="5">
         <f>SUM(G4:J4)</f>
         <v>11075</v>
       </c>
-      <c r="AD4" s="11">
+      <c r="AT4" s="5">
         <f>SUM(K4:N4)</f>
         <v>11328</v>
       </c>
-      <c r="AE4" s="11">
+      <c r="AU4" s="5">
         <f>SUM(O4:R4)</f>
         <v>12479</v>
       </c>
-      <c r="AF4" s="11">
+      <c r="AV4" s="5">
         <v>9013</v>
       </c>
-      <c r="AG4" s="11">
-        <f>SUM(W4:Z4)</f>
-        <v>10920.827300000001</v>
-      </c>
-      <c r="AH4" s="5">
-        <f t="shared" ref="AH4:AP4" si="2">AH3-AH5</f>
-        <v>11825.420970000005</v>
-      </c>
-      <c r="AI4" s="5">
-        <f t="shared" si="2"/>
-        <v>12771.454647600007</v>
-      </c>
-      <c r="AJ4" s="5">
-        <f t="shared" si="2"/>
-        <v>13410.027379980005</v>
-      </c>
-      <c r="AK4" s="5">
-        <f t="shared" si="2"/>
-        <v>14080.528748979006</v>
-      </c>
-      <c r="AL4" s="5">
-        <f t="shared" si="2"/>
-        <v>14643.749898938167</v>
-      </c>
-      <c r="AM4" s="5">
-        <f t="shared" si="2"/>
-        <v>15083.062395906312</v>
-      </c>
-      <c r="AN4" s="5">
-        <f t="shared" si="2"/>
-        <v>15535.554267783504</v>
-      </c>
-      <c r="AO4" s="5">
-        <f t="shared" si="2"/>
-        <v>16001.620895817006</v>
-      </c>
-      <c r="AP4" s="5">
-        <f t="shared" si="2"/>
-        <v>16481.669522691518</v>
+      <c r="AW4" s="5">
+        <v>11902</v>
+      </c>
+      <c r="AX4" s="5">
+        <v>14011</v>
+      </c>
+      <c r="AY4" s="5">
+        <v>15186</v>
+      </c>
+      <c r="AZ4" s="5">
+        <v>16288</v>
+      </c>
+      <c r="BA4" s="5">
+        <f t="shared" ref="BA4" si="3">BA3-BA5</f>
+        <v>16549.948800000002</v>
+      </c>
+      <c r="BB4" s="5">
+        <f t="shared" ref="AX4:BF4" si="4">BB3-BB5</f>
+        <v>16880.947776000001</v>
+      </c>
+      <c r="BC4" s="5">
+        <f t="shared" si="4"/>
+        <v>17387.376209280003</v>
+      </c>
+      <c r="BD4" s="5">
+        <f t="shared" si="4"/>
+        <v>17908.997495558404</v>
+      </c>
+      <c r="BE4" s="5">
+        <f t="shared" si="4"/>
+        <v>18446.267420425156</v>
+      </c>
+      <c r="BF4" s="5">
+        <f t="shared" si="4"/>
+        <v>18999.655443037911</v>
+      </c>
+      <c r="BG4" s="5">
+        <f t="shared" ref="BG4:BK4" si="5">BG3-BG5</f>
+        <v>19379.64855189867</v>
+      </c>
+      <c r="BH4" s="5">
+        <f t="shared" si="5"/>
+        <v>19767.241522936645</v>
+      </c>
+      <c r="BI4" s="5">
+        <f t="shared" si="5"/>
+        <v>20162.586353395378</v>
+      </c>
+      <c r="BJ4" s="5">
+        <f t="shared" si="5"/>
+        <v>20565.838080463283</v>
+      </c>
+      <c r="BK4" s="5">
+        <f t="shared" si="5"/>
+        <v>20977.154842072548</v>
       </c>
     </row>
-    <row r="5" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:164" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="10">
-        <f t="shared" ref="C5:U5" si="3">C3-C4</f>
+      <c r="C5" s="9">
+        <f t="shared" ref="C5:U5" si="6">C3-C4</f>
         <v>2834</v>
       </c>
-      <c r="D5" s="10">
-        <f t="shared" si="3"/>
+      <c r="D5" s="9">
+        <f t="shared" si="6"/>
         <v>3111</v>
       </c>
-      <c r="E5" s="10">
-        <f t="shared" si="3"/>
+      <c r="E5" s="9">
+        <f t="shared" si="6"/>
         <v>3546</v>
       </c>
-      <c r="F5" s="10">
-        <f t="shared" si="3"/>
+      <c r="F5" s="9">
+        <f t="shared" si="6"/>
         <v>3787</v>
       </c>
-      <c r="G5" s="10">
-        <f t="shared" si="3"/>
+      <c r="G5" s="9">
+        <f t="shared" si="6"/>
         <v>3240</v>
       </c>
-      <c r="H5" s="10">
-        <f t="shared" si="3"/>
+      <c r="H5" s="9">
+        <f t="shared" si="6"/>
         <v>3342</v>
       </c>
-      <c r="I5" s="10">
-        <f t="shared" si="3"/>
+      <c r="I5" s="9">
+        <f t="shared" si="6"/>
         <v>3737</v>
       </c>
-      <c r="J5" s="10">
-        <f t="shared" si="3"/>
+      <c r="J5" s="9">
+        <f t="shared" si="6"/>
         <v>3941</v>
       </c>
-      <c r="K5" s="10">
-        <f t="shared" si="3"/>
+      <c r="K5" s="9">
+        <f t="shared" si="6"/>
         <v>3328</v>
       </c>
-      <c r="L5" s="10">
-        <f t="shared" si="3"/>
+      <c r="L5" s="9">
+        <f t="shared" si="6"/>
         <v>3490</v>
       </c>
-      <c r="M5" s="10">
-        <f t="shared" si="3"/>
+      <c r="M5" s="9">
+        <f t="shared" si="6"/>
         <v>3878</v>
       </c>
-      <c r="N5" s="10">
-        <f t="shared" si="3"/>
+      <c r="N5" s="9">
+        <f t="shared" si="6"/>
         <v>4122</v>
       </c>
-      <c r="O5" s="10">
-        <f t="shared" si="3"/>
+      <c r="O5" s="9">
+        <f t="shared" si="6"/>
         <v>3525</v>
       </c>
-      <c r="P5" s="10">
-        <f t="shared" si="3"/>
+      <c r="P5" s="9">
+        <f t="shared" si="6"/>
         <v>3759</v>
       </c>
-      <c r="Q5" s="10">
-        <f t="shared" si="3"/>
+      <c r="Q5" s="9">
+        <f t="shared" si="6"/>
         <v>4254</v>
       </c>
-      <c r="R5" s="10">
-        <f t="shared" si="3"/>
+      <c r="R5" s="9">
+        <f t="shared" si="6"/>
         <v>4269</v>
       </c>
-      <c r="S5" s="10">
-        <f t="shared" si="3"/>
+      <c r="S5" s="9">
+        <f t="shared" si="6"/>
         <v>1929</v>
       </c>
-      <c r="T5" s="10">
-        <f t="shared" si="3"/>
+      <c r="T5" s="9">
+        <f t="shared" si="6"/>
         <v>2583</v>
       </c>
-      <c r="U5" s="10">
-        <f t="shared" si="3"/>
+      <c r="U5" s="9">
+        <f t="shared" si="6"/>
         <v>3660</v>
       </c>
-      <c r="V5" s="10">
+      <c r="V5" s="9">
         <f>V3*0.53</f>
         <v>3348.01</v>
       </c>
-      <c r="W5" s="10">
+      <c r="W5" s="9">
         <f>W3*0.59</f>
         <v>3020.5934999999999</v>
       </c>
-      <c r="X5" s="10">
+      <c r="X5" s="9">
         <f>X3*0.55</f>
         <v>3381.9500000000003</v>
       </c>
-      <c r="Y5" s="10">
+      <c r="Y5" s="9">
         <f>Y3*0.59</f>
         <v>3927.748</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="9">
         <f>Z3*0.53</f>
         <v>3749.7712000000006</v>
       </c>
-      <c r="AB5" s="10">
-        <f t="shared" ref="AB5:AG5" si="4">AB3-AB4</f>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9">
+        <f t="shared" ref="AI5:AJ5" si="7">AI3-AI4</f>
+        <v>4940</v>
+      </c>
+      <c r="AJ5" s="9">
+        <f t="shared" si="7"/>
+        <v>5601</v>
+      </c>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9">
+        <f t="shared" ref="AM5:AN5" si="8">AM3-AM4</f>
+        <v>5012</v>
+      </c>
+      <c r="AN5" s="9">
+        <f t="shared" si="8"/>
+        <v>5691</v>
+      </c>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AR5" s="9">
+        <f t="shared" ref="AR5:AW5" si="9">AR3-AR4</f>
         <v>13278</v>
       </c>
-      <c r="AC5" s="10">
-        <f t="shared" si="4"/>
+      <c r="AS5" s="9">
+        <f t="shared" si="9"/>
         <v>14260</v>
       </c>
-      <c r="AD5" s="10">
-        <f t="shared" si="4"/>
+      <c r="AT5" s="9">
+        <f t="shared" si="9"/>
         <v>14818</v>
       </c>
-      <c r="AE5" s="10">
-        <f t="shared" si="4"/>
+      <c r="AU5" s="9">
+        <f t="shared" si="9"/>
         <v>15807</v>
       </c>
-      <c r="AF5" s="10">
-        <f t="shared" si="4"/>
+      <c r="AV5" s="9">
+        <f t="shared" si="9"/>
         <v>11389</v>
       </c>
-      <c r="AG5" s="10">
-        <f t="shared" si="4"/>
-        <v>14080.062700000002</v>
-      </c>
-      <c r="AH5" s="10">
-        <f t="shared" ref="AH5:AP5" si="5">AH3*0.57</f>
-        <v>15675.558030000002</v>
-      </c>
-      <c r="AI5" s="10">
-        <f t="shared" si="5"/>
-        <v>16929.602672400004</v>
-      </c>
-      <c r="AJ5" s="10">
-        <f t="shared" si="5"/>
-        <v>17776.082806020007</v>
-      </c>
-      <c r="AK5" s="10">
-        <f t="shared" si="5"/>
-        <v>18664.886946321007</v>
-      </c>
-      <c r="AL5" s="10">
-        <f t="shared" si="5"/>
-        <v>19411.48242417385</v>
-      </c>
-      <c r="AM5" s="10">
-        <f t="shared" si="5"/>
-        <v>19993.826896899063</v>
-      </c>
-      <c r="AN5" s="10">
-        <f t="shared" si="5"/>
-        <v>20593.641703806032</v>
-      </c>
-      <c r="AO5" s="10">
-        <f t="shared" si="5"/>
-        <v>21211.450954920216</v>
-      </c>
-      <c r="AP5" s="10">
-        <f t="shared" si="5"/>
-        <v>21847.794483567821</v>
+      <c r="AW5" s="9">
+        <f>AW3-AW4</f>
+        <v>15814</v>
+      </c>
+      <c r="AX5" s="9">
+        <f>AX3-AX4</f>
+        <v>18558</v>
+      </c>
+      <c r="AY5" s="9">
+        <f>AY3-AY4</f>
+        <v>20761</v>
+      </c>
+      <c r="AZ5" s="9">
+        <f>AZ3-AZ4</f>
+        <v>22344</v>
+      </c>
+      <c r="BA5" s="9">
+        <f>BA3*0.58</f>
+        <v>22854.691199999997</v>
+      </c>
+      <c r="BB5" s="9">
+        <f t="shared" ref="BB5:BK5" si="10">BB3*0.58</f>
+        <v>23311.785023999997</v>
+      </c>
+      <c r="BC5" s="9">
+        <f t="shared" si="10"/>
+        <v>24011.138574719997</v>
+      </c>
+      <c r="BD5" s="9">
+        <f t="shared" si="10"/>
+        <v>24731.472731961599</v>
+      </c>
+      <c r="BE5" s="9">
+        <f t="shared" si="10"/>
+        <v>25473.41691392045</v>
+      </c>
+      <c r="BF5" s="9">
+        <f t="shared" si="10"/>
+        <v>26237.619421338066</v>
+      </c>
+      <c r="BG5" s="9">
+        <f t="shared" si="10"/>
+        <v>26762.371809764827</v>
+      </c>
+      <c r="BH5" s="9">
+        <f t="shared" si="10"/>
+        <v>27297.619245960122</v>
+      </c>
+      <c r="BI5" s="9">
+        <f t="shared" si="10"/>
+        <v>27843.571630879323</v>
+      </c>
+      <c r="BJ5" s="9">
+        <f t="shared" si="10"/>
+        <v>28400.44306349691</v>
+      </c>
+      <c r="BK5" s="9">
+        <f t="shared" si="10"/>
+        <v>28968.451924766847</v>
       </c>
     </row>
-    <row r="6" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -1530,8 +1886,8 @@
         <f>3020-T6</f>
         <v>1448</v>
       </c>
-      <c r="V6" s="11">
-        <f>AF6-U6-T6-S6</f>
+      <c r="V6" s="5">
+        <f>AV6-U6-T6-S6</f>
         <v>2339</v>
       </c>
       <c r="W6" s="5">
@@ -1550,67 +1906,109 @@
         <f>V6*1.02</f>
         <v>2385.7800000000002</v>
       </c>
-      <c r="AB6" s="11">
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5">
+        <v>2553</v>
+      </c>
+      <c r="AJ6" s="12">
+        <f t="shared" ref="AJ6:AJ8" si="11">AJ31-AI6</f>
+        <v>2914</v>
+      </c>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5">
+        <v>2612</v>
+      </c>
+      <c r="AN6" s="12">
+        <f t="shared" ref="AN6:AN8" si="12">AN31-AM6</f>
+        <v>2972</v>
+      </c>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="5"/>
+      <c r="AR6" s="5">
         <f>SUM(C6:F6)</f>
         <v>8175</v>
       </c>
-      <c r="AC6" s="11">
+      <c r="AS6" s="5">
         <f>SUM(G6:J6)</f>
         <v>8944</v>
       </c>
-      <c r="AD6" s="11">
+      <c r="AT6" s="5">
         <f>SUM(K6:N6)</f>
         <v>9328</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AU6" s="5">
         <f>SUM(O6:R6)</f>
         <v>8176</v>
       </c>
-      <c r="AF6" s="11">
+      <c r="AV6" s="5">
         <v>6807</v>
       </c>
-      <c r="AG6" s="11">
-        <f>SUM(W6:Z6)</f>
-        <v>7813.58</v>
-      </c>
-      <c r="AH6" s="5">
-        <f>AG6*1.05</f>
-        <v>8204.259</v>
-      </c>
-      <c r="AI6" s="5">
-        <f>AH6*1.03</f>
-        <v>8450.386770000001</v>
-      </c>
-      <c r="AJ6" s="5">
-        <f t="shared" ref="AJ6:AK6" si="6">AI6*1.03</f>
-        <v>8703.8983731000008</v>
-      </c>
-      <c r="AK6" s="5">
-        <f t="shared" si="6"/>
-        <v>8965.015324293001</v>
-      </c>
-      <c r="AL6" s="5">
-        <f>AK6*1.02</f>
-        <v>9144.3156307788613</v>
-      </c>
-      <c r="AM6" s="5">
-        <f t="shared" ref="AM6:AP6" si="7">AL6*1.02</f>
-        <v>9327.2019433944388</v>
-      </c>
-      <c r="AN6" s="5">
-        <f t="shared" si="7"/>
-        <v>9513.7459822623277</v>
-      </c>
-      <c r="AO6" s="5">
-        <f t="shared" si="7"/>
-        <v>9704.0209019075737</v>
-      </c>
-      <c r="AP6" s="5">
-        <f t="shared" si="7"/>
-        <v>9898.1013199457248</v>
+      <c r="AW6" s="5">
+        <v>8596</v>
+      </c>
+      <c r="AX6" s="5">
+        <v>9867</v>
+      </c>
+      <c r="AY6" s="5">
+        <v>10853</v>
+      </c>
+      <c r="AZ6" s="5">
+        <v>11555</v>
+      </c>
+      <c r="BA6" s="5">
+        <f>AZ6*1.04</f>
+        <v>12017.2</v>
+      </c>
+      <c r="BB6" s="5">
+        <f>BA6*1.03</f>
+        <v>12377.716</v>
+      </c>
+      <c r="BC6" s="5">
+        <f t="shared" ref="BC6:BF6" si="13">BB6*1.02</f>
+        <v>12625.270320000001</v>
+      </c>
+      <c r="BD6" s="5">
+        <f t="shared" si="13"/>
+        <v>12877.775726400001</v>
+      </c>
+      <c r="BE6" s="5">
+        <f t="shared" si="13"/>
+        <v>13135.331240928001</v>
+      </c>
+      <c r="BF6" s="5">
+        <f t="shared" si="13"/>
+        <v>13398.037865746561</v>
+      </c>
+      <c r="BG6" s="5">
+        <f t="shared" ref="BG6" si="14">BF6*1.02</f>
+        <v>13665.998623061492</v>
+      </c>
+      <c r="BH6" s="5">
+        <f t="shared" ref="BH6" si="15">BG6*1.02</f>
+        <v>13939.318595522722</v>
+      </c>
+      <c r="BI6" s="5">
+        <f t="shared" ref="BI6" si="16">BH6*1.02</f>
+        <v>14218.104967433177</v>
+      </c>
+      <c r="BJ6" s="5">
+        <f t="shared" ref="BJ6" si="17">BI6*1.02</f>
+        <v>14502.467066781841</v>
+      </c>
+      <c r="BK6" s="5">
+        <f t="shared" ref="BK6" si="18">BJ6*1.02</f>
+        <v>14792.516408117477</v>
       </c>
     </row>
-    <row r="7" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -1673,8 +2071,8 @@
         <f>6-T7</f>
         <v>2</v>
       </c>
-      <c r="V7" s="11">
-        <f>AF7-U7-T7-S7</f>
+      <c r="V7" s="5">
+        <f>AV7-U7-T7-S7</f>
         <v>23</v>
       </c>
       <c r="W7" s="5">
@@ -1689,67 +2087,109 @@
       <c r="Z7" s="5">
         <v>20</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5">
+        <v>17</v>
+      </c>
+      <c r="AJ7" s="12">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
+      <c r="AM7" s="5">
+        <v>6</v>
+      </c>
+      <c r="AN7" s="12">
+        <f t="shared" si="12"/>
+        <v>-1</v>
+      </c>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AR7" s="5">
         <f>SUM(C7:F7)</f>
         <v>20</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AS7" s="5">
         <f>SUM(G7:J7)</f>
         <v>38</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AT7" s="5">
         <f>SUM(K7:N7)</f>
         <v>30</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AU7" s="5">
         <f>SUM(O7:R7)</f>
         <v>33</v>
       </c>
-      <c r="AF7" s="11">
+      <c r="AV7" s="5">
         <v>31</v>
       </c>
-      <c r="AG7" s="11">
-        <f>SUM(W7:Z7)</f>
-        <v>29</v>
-      </c>
-      <c r="AH7" s="5">
-        <f t="shared" ref="AH7:AP7" si="8">25*1.01</f>
-        <v>25.25</v>
-      </c>
-      <c r="AI7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AJ7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AK7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AL7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AM7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AN7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AO7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
-      </c>
-      <c r="AP7" s="5">
-        <f t="shared" si="8"/>
-        <v>25.25</v>
+      <c r="AW7" s="5">
+        <v>35</v>
+      </c>
+      <c r="AX7" s="5">
+        <v>43</v>
+      </c>
+      <c r="AY7" s="5">
+        <v>59</v>
+      </c>
+      <c r="AZ7" s="5">
+        <v>60</v>
+      </c>
+      <c r="BA7" s="5">
+        <f>AZ7*1.05</f>
+        <v>63</v>
+      </c>
+      <c r="BB7" s="5">
+        <f t="shared" ref="BB7:BK7" si="19">BA7*1.05</f>
+        <v>66.150000000000006</v>
+      </c>
+      <c r="BC7" s="5">
+        <f t="shared" si="19"/>
+        <v>69.45750000000001</v>
+      </c>
+      <c r="BD7" s="5">
+        <f t="shared" si="19"/>
+        <v>72.930375000000012</v>
+      </c>
+      <c r="BE7" s="5">
+        <f t="shared" si="19"/>
+        <v>76.576893750000011</v>
+      </c>
+      <c r="BF7" s="5">
+        <f t="shared" si="19"/>
+        <v>80.40573843750002</v>
+      </c>
+      <c r="BG7" s="5">
+        <f t="shared" si="19"/>
+        <v>84.426025359375018</v>
+      </c>
+      <c r="BH7" s="5">
+        <f t="shared" si="19"/>
+        <v>88.647326627343773</v>
+      </c>
+      <c r="BI7" s="5">
+        <f t="shared" si="19"/>
+        <v>93.079692958710964</v>
+      </c>
+      <c r="BJ7" s="5">
+        <f t="shared" si="19"/>
+        <v>97.733677606646523</v>
+      </c>
+      <c r="BK7" s="5">
+        <f t="shared" si="19"/>
+        <v>102.62036148697885</v>
       </c>
     </row>
-    <row r="8" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -1812,8 +2252,8 @@
         <f>1684-T8</f>
         <v>992</v>
       </c>
-      <c r="V8" s="11">
-        <f>AF8-U8-T8-S8</f>
+      <c r="V8" s="5">
+        <f>AV8-U8-T8-S8</f>
         <v>369</v>
       </c>
       <c r="W8" s="5">
@@ -1828,228 +2268,319 @@
       <c r="Z8" s="5">
         <v>750</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5">
+        <v>734</v>
+      </c>
+      <c r="AJ8" s="12">
+        <f t="shared" si="11"/>
+        <v>765</v>
+      </c>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
+      <c r="AM8" s="5">
+        <v>752</v>
+      </c>
+      <c r="AN8" s="12">
+        <f t="shared" si="12"/>
+        <v>790</v>
+      </c>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AR8" s="5">
         <f>SUM(C8:F8)</f>
         <v>1062</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AS8" s="5">
         <f>SUM(G8:J8)</f>
         <v>963</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AT8" s="5">
         <f>SUM(K8:N8)</f>
         <v>1101</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AU8" s="5">
         <f>SUM(O8:R8)</f>
         <v>2827</v>
       </c>
-      <c r="AF8" s="11">
+      <c r="AV8" s="5">
         <v>3045</v>
       </c>
-      <c r="AG8" s="11">
-        <f>SUM(W8:Z8)</f>
-        <v>3000</v>
-      </c>
-      <c r="AH8" s="5">
-        <f t="shared" ref="AH8:AK8" si="9">AG8*1.05</f>
-        <v>3150</v>
-      </c>
-      <c r="AI8" s="5">
-        <f t="shared" si="9"/>
-        <v>3307.5</v>
-      </c>
-      <c r="AJ8" s="5">
-        <f t="shared" si="9"/>
-        <v>3472.875</v>
-      </c>
-      <c r="AK8" s="5">
-        <f t="shared" si="9"/>
-        <v>3646.5187500000002</v>
-      </c>
-      <c r="AL8" s="5">
-        <f>AK8*1.03</f>
-        <v>3755.9143125000005</v>
-      </c>
-      <c r="AM8" s="5">
-        <f t="shared" ref="AM8:AP8" si="10">AL8*1.03</f>
-        <v>3868.5917418750005</v>
-      </c>
-      <c r="AN8" s="5">
-        <f t="shared" si="10"/>
-        <v>3984.6494941312508</v>
-      </c>
-      <c r="AO8" s="5">
-        <f t="shared" si="10"/>
-        <v>4104.1889789551888</v>
-      </c>
-      <c r="AP8" s="5">
-        <f t="shared" si="10"/>
-        <v>4227.3146483238443</v>
+      <c r="AW8" s="5">
+        <v>2901</v>
+      </c>
+      <c r="AX8" s="5">
+        <f>231+2899</f>
+        <v>3130</v>
+      </c>
+      <c r="AY8" s="5">
+        <v>3041</v>
+      </c>
+      <c r="AZ8" s="5">
+        <v>3174</v>
+      </c>
+      <c r="BA8" s="5">
+        <f>AZ8*1.03</f>
+        <v>3269.2200000000003</v>
+      </c>
+      <c r="BB8" s="5">
+        <f>BA8*1.03</f>
+        <v>3367.2966000000001</v>
+      </c>
+      <c r="BC8" s="5">
+        <f t="shared" ref="BC8:BF8" si="20">BB8*1.03</f>
+        <v>3468.3154980000004</v>
+      </c>
+      <c r="BD8" s="5">
+        <f t="shared" si="20"/>
+        <v>3572.3649629400006</v>
+      </c>
+      <c r="BE8" s="5">
+        <f t="shared" si="20"/>
+        <v>3679.5359118282008</v>
+      </c>
+      <c r="BF8" s="5">
+        <f t="shared" si="20"/>
+        <v>3789.9219891830471</v>
+      </c>
+      <c r="BG8" s="5">
+        <f t="shared" ref="BG8" si="21">BF8*1.03</f>
+        <v>3903.6196488585388</v>
+      </c>
+      <c r="BH8" s="5">
+        <f t="shared" ref="BH8" si="22">BG8*1.03</f>
+        <v>4020.728238324295</v>
+      </c>
+      <c r="BI8" s="5">
+        <f t="shared" ref="BI8" si="23">BH8*1.03</f>
+        <v>4141.3500854740241</v>
+      </c>
+      <c r="BJ8" s="5">
+        <f t="shared" ref="BJ8" si="24">BI8*1.03</f>
+        <v>4265.5905880382452</v>
+      </c>
+      <c r="BK8" s="5">
+        <f t="shared" ref="BK8" si="25">BJ8*1.03</f>
+        <v>4393.558305679393</v>
       </c>
     </row>
-    <row r="9" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:164" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10">
-        <f t="shared" ref="C9:Z9" si="11">C5-C6-C7-C8</f>
+      <c r="C9" s="9">
+        <f t="shared" ref="C9:Z9" si="26">C5-C6-C7-C8</f>
         <v>705</v>
       </c>
-      <c r="D9" s="10">
-        <f t="shared" si="11"/>
+      <c r="D9" s="9">
+        <f t="shared" si="26"/>
         <v>900</v>
       </c>
-      <c r="E9" s="10">
-        <f t="shared" si="11"/>
+      <c r="E9" s="9">
+        <f t="shared" si="26"/>
         <v>1217</v>
       </c>
-      <c r="F9" s="10">
-        <f t="shared" si="11"/>
+      <c r="F9" s="9">
+        <f t="shared" si="26"/>
         <v>1199</v>
       </c>
-      <c r="G9" s="10">
-        <f t="shared" si="11"/>
+      <c r="G9" s="9">
+        <f t="shared" si="26"/>
         <v>834</v>
       </c>
-      <c r="H9" s="10">
-        <f t="shared" si="11"/>
+      <c r="H9" s="9">
+        <f t="shared" si="26"/>
         <v>910</v>
       </c>
-      <c r="I9" s="10">
-        <f t="shared" si="11"/>
+      <c r="I9" s="9">
+        <f t="shared" si="26"/>
         <v>1250</v>
       </c>
-      <c r="J9" s="10">
-        <f t="shared" si="11"/>
+      <c r="J9" s="9">
+        <f t="shared" si="26"/>
         <v>1321</v>
       </c>
-      <c r="K9" s="10">
-        <f t="shared" si="11"/>
+      <c r="K9" s="9">
+        <f t="shared" si="26"/>
         <v>852</v>
       </c>
-      <c r="L9" s="10">
-        <f t="shared" si="11"/>
+      <c r="L9" s="9">
+        <f t="shared" si="26"/>
         <v>933</v>
       </c>
-      <c r="M9" s="10">
-        <f t="shared" si="11"/>
+      <c r="M9" s="9">
+        <f t="shared" si="26"/>
         <v>1287</v>
       </c>
-      <c r="N9" s="10">
-        <f t="shared" si="11"/>
+      <c r="N9" s="9">
+        <f t="shared" si="26"/>
         <v>1287</v>
       </c>
-      <c r="O9" s="10">
-        <f t="shared" si="11"/>
+      <c r="O9" s="9">
+        <f t="shared" si="26"/>
         <v>979</v>
       </c>
-      <c r="P9" s="10">
-        <f t="shared" si="11"/>
+      <c r="P9" s="9">
+        <f t="shared" si="26"/>
         <v>1060</v>
       </c>
-      <c r="Q9" s="10">
-        <f t="shared" si="11"/>
+      <c r="Q9" s="9">
+        <f t="shared" si="26"/>
         <v>1508</v>
       </c>
-      <c r="R9" s="10">
-        <f t="shared" si="11"/>
+      <c r="R9" s="9">
+        <f t="shared" si="26"/>
         <v>1224</v>
       </c>
-      <c r="S9" s="10">
-        <f t="shared" si="11"/>
+      <c r="S9" s="9">
+        <f t="shared" si="26"/>
         <v>-513</v>
       </c>
-      <c r="T9" s="10">
-        <f t="shared" si="11"/>
+      <c r="T9" s="9">
+        <f t="shared" si="26"/>
         <v>315</v>
       </c>
-      <c r="U9" s="10">
-        <f t="shared" si="11"/>
+      <c r="U9" s="9">
+        <f t="shared" si="26"/>
         <v>1218</v>
       </c>
-      <c r="V9" s="10">
-        <f t="shared" si="11"/>
+      <c r="V9" s="9">
+        <f t="shared" si="26"/>
         <v>617.01000000000022</v>
       </c>
-      <c r="W9" s="10">
-        <f t="shared" si="11"/>
+      <c r="W9" s="9">
+        <f t="shared" si="26"/>
         <v>529.99350000000004</v>
       </c>
-      <c r="X9" s="10">
-        <f t="shared" si="11"/>
+      <c r="X9" s="9">
+        <f t="shared" si="26"/>
         <v>821.15000000000032</v>
       </c>
-      <c r="Y9" s="10">
-        <f t="shared" si="11"/>
+      <c r="Y9" s="9">
+        <f t="shared" si="26"/>
         <v>1292.348</v>
       </c>
-      <c r="Z9" s="10">
-        <f t="shared" si="11"/>
+      <c r="Z9" s="9">
+        <f t="shared" si="26"/>
         <v>593.99120000000039</v>
       </c>
-      <c r="AB9" s="10">
-        <f t="shared" ref="AB9:AF9" si="12">AB5-AB6-AB7-AB8</f>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
+      <c r="AI9" s="9">
+        <f t="shared" ref="AI9:AJ9" si="27">AI5-AI6-AI7-AI8</f>
+        <v>1636</v>
+      </c>
+      <c r="AJ9" s="9">
+        <f t="shared" si="27"/>
+        <v>1905</v>
+      </c>
+      <c r="AK9" s="9"/>
+      <c r="AL9" s="9"/>
+      <c r="AM9" s="9">
+        <f t="shared" ref="AM9:AN9" si="28">AM5-AM6-AM7-AM8</f>
+        <v>1642</v>
+      </c>
+      <c r="AN9" s="9">
+        <f t="shared" si="28"/>
+        <v>1930</v>
+      </c>
+      <c r="AO9" s="9"/>
+      <c r="AP9" s="9"/>
+      <c r="AR9" s="9">
+        <f t="shared" ref="AR9:AW9" si="29">AR5-AR6-AR7-AR8</f>
         <v>4021</v>
       </c>
-      <c r="AC9" s="10">
-        <f t="shared" si="12"/>
+      <c r="AS9" s="9">
+        <f t="shared" si="29"/>
         <v>4315</v>
       </c>
-      <c r="AD9" s="10">
-        <f t="shared" si="12"/>
+      <c r="AT9" s="9">
+        <f t="shared" si="29"/>
         <v>4359</v>
       </c>
-      <c r="AE9" s="10">
-        <f t="shared" si="12"/>
+      <c r="AU9" s="9">
+        <f t="shared" si="29"/>
         <v>4771</v>
       </c>
-      <c r="AF9" s="10">
-        <f t="shared" si="12"/>
+      <c r="AV9" s="9">
+        <f t="shared" si="29"/>
         <v>1506</v>
       </c>
-      <c r="AG9" s="10">
-        <f t="shared" ref="AG9" si="13">AG5-AG6-AG7-AG8</f>
-        <v>3237.4827000000023</v>
-      </c>
-      <c r="AH9" s="10">
-        <f t="shared" ref="AH9" si="14">AH5-AH6-AH7-AH8</f>
-        <v>4296.0490300000019</v>
-      </c>
-      <c r="AI9" s="10">
-        <f t="shared" ref="AI9" si="15">AI5-AI6-AI7-AI8</f>
-        <v>5146.465902400003</v>
-      </c>
-      <c r="AJ9" s="10">
-        <f t="shared" ref="AJ9" si="16">AJ5-AJ6-AJ7-AJ8</f>
-        <v>5574.0594329200067</v>
-      </c>
-      <c r="AK9" s="10">
-        <f t="shared" ref="AK9" si="17">AK5-AK6-AK7-AK8</f>
-        <v>6028.1028720280055</v>
-      </c>
-      <c r="AL9" s="10">
-        <f t="shared" ref="AL9" si="18">AL5-AL6-AL7-AL8</f>
-        <v>6486.0024808949875</v>
-      </c>
-      <c r="AM9" s="10">
-        <f t="shared" ref="AM9" si="19">AM5-AM6-AM7-AM8</f>
-        <v>6772.783211629624</v>
-      </c>
-      <c r="AN9" s="10">
-        <f t="shared" ref="AN9" si="20">AN5-AN6-AN7-AN8</f>
-        <v>7069.9962274124537</v>
-      </c>
-      <c r="AO9" s="10">
-        <f t="shared" ref="AO9" si="21">AO5-AO6-AO7-AO8</f>
-        <v>7377.9910740574533</v>
-      </c>
-      <c r="AP9" s="10">
-        <f t="shared" ref="AP9" si="22">AP5-AP6-AP7-AP8</f>
-        <v>7697.1285152982518</v>
+      <c r="AW9" s="9">
+        <f t="shared" si="29"/>
+        <v>4282</v>
+      </c>
+      <c r="AX9" s="9">
+        <f t="shared" ref="AX9:AZ9" si="30">AX5-AX6-AX7-AX8</f>
+        <v>5518</v>
+      </c>
+      <c r="AY9" s="9">
+        <f t="shared" si="30"/>
+        <v>6808</v>
+      </c>
+      <c r="AZ9" s="9">
+        <f t="shared" si="30"/>
+        <v>7555</v>
+      </c>
+      <c r="BA9" s="9">
+        <f t="shared" ref="BA9:BB9" si="31">BA5-BA6-BA7-BA8</f>
+        <v>7505.2711999999965</v>
+      </c>
+      <c r="BB9" s="9">
+        <f t="shared" si="31"/>
+        <v>7500.6224239999974</v>
+      </c>
+      <c r="BC9" s="9">
+        <f t="shared" ref="BC9" si="32">BC5-BC6-BC7-BC8</f>
+        <v>7848.0952567199947</v>
+      </c>
+      <c r="BD9" s="9">
+        <f t="shared" ref="BD9" si="33">BD5-BD6-BD7-BD8</f>
+        <v>8208.4016676215979</v>
+      </c>
+      <c r="BE9" s="9">
+        <f t="shared" ref="BE9" si="34">BE5-BE6-BE7-BE8</f>
+        <v>8581.972867414248</v>
+      </c>
+      <c r="BF9" s="9">
+        <f t="shared" ref="BF9:BK9" si="35">BF5-BF6-BF7-BF8</f>
+        <v>8969.2538279709588</v>
+      </c>
+      <c r="BG9" s="9">
+        <f t="shared" si="35"/>
+        <v>9108.3275124854208</v>
+      </c>
+      <c r="BH9" s="9">
+        <f t="shared" si="35"/>
+        <v>9248.9250854857619</v>
+      </c>
+      <c r="BI9" s="9">
+        <f t="shared" si="35"/>
+        <v>9391.0368850134109</v>
+      </c>
+      <c r="BJ9" s="9">
+        <f t="shared" si="35"/>
+        <v>9534.6517310701784</v>
+      </c>
+      <c r="BK9" s="9">
+        <f t="shared" si="35"/>
+        <v>9679.7568494829975</v>
       </c>
     </row>
-    <row r="10" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>38</v>
       </c>
@@ -2126,8 +2657,8 @@
         <f>76-11-T10</f>
         <v>31</v>
       </c>
-      <c r="V10" s="11">
-        <f>AF10-U10-T10-S10</f>
+      <c r="V10" s="5">
+        <f>AV10-U10-T10-S10</f>
         <v>10</v>
       </c>
       <c r="W10" s="5">
@@ -2142,229 +2673,325 @@
       <c r="Z10" s="5">
         <v>10</v>
       </c>
-      <c r="AB10" s="11">
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5">
+        <f>-21-14</f>
+        <v>-35</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AJ35-AI10</f>
+        <v>-22</v>
+      </c>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5">
+        <f>-5-25</f>
+        <v>-30</v>
+      </c>
+      <c r="AN10" s="12">
+        <f>AN35-AM10</f>
+        <v>0</v>
+      </c>
+      <c r="AO10" s="5"/>
+      <c r="AP10" s="5"/>
+      <c r="AR10" s="5">
         <f>SUM(C10:F10)</f>
         <v>-58</v>
       </c>
-      <c r="AC10" s="11">
+      <c r="AS10" s="5">
         <f>SUM(G10:J10)</f>
         <v>-37</v>
       </c>
-      <c r="AD10" s="11">
+      <c r="AT10" s="5">
         <f>SUM(K10:N10)</f>
         <v>-72</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AU10" s="5">
         <f>SUM(O10:R10)</f>
         <v>91</v>
       </c>
-      <c r="AF10" s="11">
+      <c r="AV10" s="5">
         <f>139-33</f>
         <v>106</v>
       </c>
-      <c r="AG10" s="11">
-        <f>SUM(W10:Z10)</f>
-        <v>100</v>
-      </c>
-      <c r="AH10" s="5">
-        <f t="shared" ref="AH10:AJ10" si="23">AG10*0.8</f>
-        <v>80</v>
-      </c>
-      <c r="AI10" s="5">
-        <f t="shared" si="23"/>
-        <v>64</v>
-      </c>
-      <c r="AJ10" s="5">
-        <f t="shared" si="23"/>
-        <v>51.2</v>
-      </c>
-      <c r="AK10" s="5">
-        <f>AJ10*0.8</f>
-        <v>40.960000000000008</v>
-      </c>
-      <c r="AL10" s="5">
-        <f>AK10*0.8</f>
-        <v>32.768000000000008</v>
-      </c>
-      <c r="AM10" s="5">
-        <f>AL13*0.01</f>
-        <v>50.335228950980898</v>
-      </c>
-      <c r="AN10" s="5">
-        <f t="shared" ref="AN10:AP10" si="24">AM13*0.01</f>
-        <v>52.435094264893415</v>
-      </c>
-      <c r="AO10" s="5">
-        <f t="shared" si="24"/>
-        <v>54.736976838550973</v>
-      </c>
-      <c r="AP10" s="5">
-        <f t="shared" si="24"/>
-        <v>57.121381958307438</v>
+      <c r="AW10" s="5">
+        <f>142-58</f>
+        <v>84</v>
+      </c>
+      <c r="AX10" s="5">
+        <f>214-53</f>
+        <v>161</v>
+      </c>
+      <c r="AY10" s="5">
+        <f>11-72</f>
+        <v>-61</v>
+      </c>
+      <c r="AZ10" s="5">
+        <f>77-99</f>
+        <v>-22</v>
+      </c>
+      <c r="BA10" s="5">
+        <f>AZ10*0.8</f>
+        <v>-17.600000000000001</v>
+      </c>
+      <c r="BB10" s="5">
+        <f>BA10*0.8</f>
+        <v>-14.080000000000002</v>
+      </c>
+      <c r="BC10" s="5">
+        <f>BB13*0.01</f>
+        <v>58.614678907199981</v>
+      </c>
+      <c r="BD10" s="5">
+        <f t="shared" ref="BD10:BF10" si="36">BC13*0.01</f>
+        <v>60.757948506939805</v>
+      </c>
+      <c r="BE10" s="5">
+        <f t="shared" si="36"/>
+        <v>63.551621009094333</v>
+      </c>
+      <c r="BF10" s="5">
+        <f t="shared" si="36"/>
+        <v>66.443685721960208</v>
+      </c>
+      <c r="BG10" s="5">
+        <f t="shared" ref="BG10" si="37">BF13*0.01</f>
+        <v>69.441919109542184</v>
+      </c>
+      <c r="BH10" s="5">
+        <f t="shared" ref="BH10" si="38">BG13*0.01</f>
+        <v>70.503307628331854</v>
+      </c>
+      <c r="BI10" s="5">
+        <f t="shared" ref="BI10" si="39">BH13*0.01</f>
+        <v>71.591689867287954</v>
+      </c>
+      <c r="BJ10" s="5">
+        <f t="shared" ref="BJ10" si="40">BI13*0.01</f>
+        <v>72.691672522139768</v>
+      </c>
+      <c r="BK10" s="5">
+        <f t="shared" ref="BK10" si="41">BJ13*0.01</f>
+        <v>73.803288456674707</v>
       </c>
     </row>
-    <row r="11" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:164" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="10">
-        <f t="shared" ref="C11:Z11" si="25">C9-C10</f>
+      <c r="C11" s="9">
+        <f t="shared" ref="C11:Z11" si="42">C9-C10</f>
         <v>719</v>
       </c>
-      <c r="D11" s="10">
-        <f t="shared" si="25"/>
+      <c r="D11" s="9">
+        <f t="shared" si="42"/>
         <v>909</v>
       </c>
-      <c r="E11" s="10">
-        <f t="shared" si="25"/>
+      <c r="E11" s="9">
+        <f t="shared" si="42"/>
         <v>1231</v>
       </c>
-      <c r="F11" s="10">
-        <f t="shared" si="25"/>
+      <c r="F11" s="9">
+        <f t="shared" si="42"/>
         <v>1220</v>
       </c>
-      <c r="G11" s="10">
-        <f t="shared" si="25"/>
+      <c r="G11" s="9">
+        <f t="shared" si="42"/>
         <v>843</v>
       </c>
-      <c r="H11" s="10">
-        <f t="shared" si="25"/>
+      <c r="H11" s="9">
+        <f t="shared" si="42"/>
         <v>919</v>
       </c>
-      <c r="I11" s="10">
-        <f t="shared" si="25"/>
+      <c r="I11" s="9">
+        <f t="shared" si="42"/>
         <v>1262</v>
       </c>
-      <c r="J11" s="10">
-        <f t="shared" si="25"/>
+      <c r="J11" s="9">
+        <f t="shared" si="42"/>
         <v>1328</v>
       </c>
-      <c r="K11" s="10">
-        <f t="shared" si="25"/>
+      <c r="K11" s="9">
+        <f t="shared" si="42"/>
         <v>867</v>
       </c>
-      <c r="L11" s="10">
-        <f t="shared" si="25"/>
+      <c r="L11" s="9">
+        <f t="shared" si="42"/>
         <v>958</v>
       </c>
-      <c r="M11" s="10">
-        <f t="shared" si="25"/>
+      <c r="M11" s="9">
+        <f t="shared" si="42"/>
         <v>1291</v>
       </c>
-      <c r="N11" s="10">
-        <f t="shared" si="25"/>
+      <c r="N11" s="9">
+        <f t="shared" si="42"/>
         <v>1315</v>
       </c>
-      <c r="O11" s="10">
-        <f t="shared" si="25"/>
+      <c r="O11" s="9">
+        <f t="shared" si="42"/>
         <v>952</v>
       </c>
-      <c r="P11" s="10">
-        <f t="shared" si="25"/>
+      <c r="P11" s="9">
+        <f t="shared" si="42"/>
         <v>1034</v>
       </c>
-      <c r="Q11" s="10">
-        <f t="shared" si="25"/>
+      <c r="Q11" s="9">
+        <f t="shared" si="42"/>
         <v>1486</v>
       </c>
-      <c r="R11" s="10">
-        <f t="shared" si="25"/>
+      <c r="R11" s="9">
+        <f t="shared" si="42"/>
         <v>1208</v>
       </c>
-      <c r="S11" s="10">
-        <f t="shared" si="25"/>
+      <c r="S11" s="9">
+        <f t="shared" si="42"/>
         <v>-544</v>
       </c>
-      <c r="T11" s="10">
-        <f t="shared" si="25"/>
+      <c r="T11" s="9">
+        <f t="shared" si="42"/>
         <v>281</v>
       </c>
-      <c r="U11" s="10">
-        <f t="shared" si="25"/>
+      <c r="U11" s="9">
+        <f t="shared" si="42"/>
         <v>1187</v>
       </c>
-      <c r="V11" s="10">
-        <f t="shared" si="25"/>
+      <c r="V11" s="9">
+        <f t="shared" si="42"/>
         <v>607.01000000000022</v>
       </c>
-      <c r="W11" s="10">
-        <f t="shared" si="25"/>
+      <c r="W11" s="9">
+        <f t="shared" si="42"/>
         <v>499.99350000000004</v>
       </c>
-      <c r="X11" s="10">
-        <f t="shared" si="25"/>
+      <c r="X11" s="9">
+        <f t="shared" si="42"/>
         <v>791.15000000000032</v>
       </c>
-      <c r="Y11" s="10">
-        <f t="shared" si="25"/>
+      <c r="Y11" s="9">
+        <f t="shared" si="42"/>
         <v>1262.348</v>
       </c>
-      <c r="Z11" s="10">
-        <f t="shared" si="25"/>
+      <c r="Z11" s="9">
+        <f t="shared" si="42"/>
         <v>583.99120000000039</v>
       </c>
-      <c r="AB11" s="10">
-        <f t="shared" ref="AB11:AF11" si="26">AB9-AB10</f>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="9"/>
+      <c r="AH11" s="9"/>
+      <c r="AI11" s="9">
+        <f t="shared" ref="AI11:AJ11" si="43">AI9-AI10</f>
+        <v>1671</v>
+      </c>
+      <c r="AJ11" s="9">
+        <f t="shared" si="43"/>
+        <v>1927</v>
+      </c>
+      <c r="AK11" s="9"/>
+      <c r="AL11" s="9"/>
+      <c r="AM11" s="9">
+        <f t="shared" ref="AM11:AN11" si="44">AM9-AM10</f>
+        <v>1672</v>
+      </c>
+      <c r="AN11" s="9">
+        <f t="shared" si="44"/>
+        <v>1930</v>
+      </c>
+      <c r="AO11" s="9"/>
+      <c r="AP11" s="9"/>
+      <c r="AR11" s="9">
+        <f t="shared" ref="AR11:AW11" si="45">AR9-AR10</f>
         <v>4079</v>
       </c>
-      <c r="AC11" s="10">
-        <f t="shared" si="26"/>
+      <c r="AS11" s="9">
+        <f t="shared" si="45"/>
         <v>4352</v>
       </c>
-      <c r="AD11" s="10">
-        <f t="shared" si="26"/>
+      <c r="AT11" s="9">
+        <f t="shared" si="45"/>
         <v>4431</v>
       </c>
-      <c r="AE11" s="10">
-        <f t="shared" si="26"/>
+      <c r="AU11" s="9">
+        <f t="shared" si="45"/>
         <v>4680</v>
       </c>
-      <c r="AF11" s="10">
-        <f t="shared" si="26"/>
+      <c r="AV11" s="9">
+        <f t="shared" si="45"/>
         <v>1400</v>
       </c>
-      <c r="AG11" s="10">
-        <f t="shared" ref="AG11" si="27">AG9-AG10</f>
-        <v>3137.4827000000023</v>
-      </c>
-      <c r="AH11" s="10">
-        <f t="shared" ref="AH11" si="28">AH9-AH10</f>
-        <v>4216.0490300000019</v>
-      </c>
-      <c r="AI11" s="10">
-        <f t="shared" ref="AI11" si="29">AI9-AI10</f>
-        <v>5082.465902400003</v>
-      </c>
-      <c r="AJ11" s="10">
-        <f t="shared" ref="AJ11" si="30">AJ9-AJ10</f>
-        <v>5522.8594329200068</v>
-      </c>
-      <c r="AK11" s="10">
-        <f t="shared" ref="AK11" si="31">AK9-AK10</f>
-        <v>5987.1428720280055</v>
-      </c>
-      <c r="AL11" s="10">
-        <f t="shared" ref="AL11" si="32">AL9-AL10</f>
-        <v>6453.2344808949874</v>
-      </c>
-      <c r="AM11" s="10">
-        <f t="shared" ref="AM11" si="33">AM9-AM10</f>
-        <v>6722.4479826786428</v>
-      </c>
-      <c r="AN11" s="10">
-        <f t="shared" ref="AN11" si="34">AN9-AN10</f>
-        <v>7017.5611331475602</v>
-      </c>
-      <c r="AO11" s="10">
-        <f t="shared" ref="AO11" si="35">AO9-AO10</f>
-        <v>7323.2540972189026</v>
-      </c>
-      <c r="AP11" s="10">
-        <f t="shared" ref="AP11" si="36">AP9-AP10</f>
-        <v>7640.0071333399446</v>
+      <c r="AW11" s="9">
+        <f t="shared" si="45"/>
+        <v>4198</v>
+      </c>
+      <c r="AX11" s="9">
+        <f t="shared" ref="AX11:AZ11" si="46">AX9-AX10</f>
+        <v>5357</v>
+      </c>
+      <c r="AY11" s="9">
+        <f t="shared" si="46"/>
+        <v>6869</v>
+      </c>
+      <c r="AZ11" s="9">
+        <f t="shared" si="46"/>
+        <v>7577</v>
+      </c>
+      <c r="BA11" s="9">
+        <f t="shared" ref="BA11:BB11" si="47">BA9-BA10</f>
+        <v>7522.8711999999969</v>
+      </c>
+      <c r="BB11" s="9">
+        <f t="shared" si="47"/>
+        <v>7514.7024239999973</v>
+      </c>
+      <c r="BC11" s="9">
+        <f t="shared" ref="BC11" si="48">BC9-BC10</f>
+        <v>7789.4805778127948</v>
+      </c>
+      <c r="BD11" s="9">
+        <f t="shared" ref="BD11" si="49">BD9-BD10</f>
+        <v>8147.6437191146579</v>
+      </c>
+      <c r="BE11" s="9">
+        <f t="shared" ref="BE11" si="50">BE9-BE10</f>
+        <v>8518.4212464051543</v>
+      </c>
+      <c r="BF11" s="9">
+        <f t="shared" ref="BF11:BK11" si="51">BF9-BF10</f>
+        <v>8902.8101422489981</v>
+      </c>
+      <c r="BG11" s="9">
+        <f t="shared" si="51"/>
+        <v>9038.8855933758787</v>
+      </c>
+      <c r="BH11" s="9">
+        <f t="shared" si="51"/>
+        <v>9178.4217778574293</v>
+      </c>
+      <c r="BI11" s="9">
+        <f t="shared" si="51"/>
+        <v>9319.4451951461233</v>
+      </c>
+      <c r="BJ11" s="9">
+        <f t="shared" si="51"/>
+        <v>9461.9600585480384</v>
+      </c>
+      <c r="BK11" s="9">
+        <f t="shared" si="51"/>
+        <v>9605.9535610263229</v>
       </c>
     </row>
-    <row r="12" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>40</v>
       </c>
@@ -2427,8 +3054,8 @@
         <f>-65-T12</f>
         <v>-130</v>
       </c>
-      <c r="V12" s="11">
-        <f>AF12-U12-T12-S12</f>
+      <c r="V12" s="5">
+        <f>AV12-U12-T12-S12</f>
         <v>490</v>
       </c>
       <c r="W12" s="5">
@@ -2436,643 +3063,733 @@
         <v>109.99857000000002</v>
       </c>
       <c r="X12" s="5">
-        <f t="shared" ref="X12:Z12" si="37">X11*0.22</f>
+        <f t="shared" ref="X12:Z12" si="52">X11*0.22</f>
         <v>174.05300000000008</v>
       </c>
       <c r="Y12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="52"/>
         <v>277.71656000000002</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="52"/>
         <v>128.47806400000007</v>
       </c>
-      <c r="AB12" s="11">
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="5">
+        <v>373</v>
+      </c>
+      <c r="AJ12" s="12">
+        <f>AJ37-AI12</f>
+        <v>447</v>
+      </c>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5">
+        <v>366</v>
+      </c>
+      <c r="AN12" s="12">
+        <f>AN37-AM12</f>
+        <v>444</v>
+      </c>
+      <c r="AO12" s="5"/>
+      <c r="AP12" s="5"/>
+      <c r="AR12" s="5">
         <f>SUM(C12:F12)</f>
         <v>917</v>
       </c>
-      <c r="AC12" s="11">
+      <c r="AS12" s="5">
         <f>SUM(G12:J12)</f>
         <v>980</v>
       </c>
-      <c r="AD12" s="11">
+      <c r="AT12" s="5">
         <f>SUM(K12:N12)</f>
         <v>980</v>
       </c>
-      <c r="AE12" s="11">
+      <c r="AU12" s="5">
         <f>SUM(O12:R12)</f>
         <v>1033</v>
       </c>
-      <c r="AF12" s="11">
+      <c r="AV12" s="5">
         <v>295</v>
       </c>
-      <c r="AG12" s="11">
-        <f>SUM(W12:Z12)</f>
-        <v>690.24619400000029</v>
-      </c>
-      <c r="AH12" s="5">
-        <f t="shared" ref="AH12:AP12" si="38">AH11*0.22</f>
-        <v>927.5307866000004</v>
-      </c>
-      <c r="AI12" s="5">
-        <f t="shared" si="38"/>
-        <v>1118.1424985280007</v>
-      </c>
-      <c r="AJ12" s="5">
-        <f t="shared" si="38"/>
-        <v>1215.0290752424014</v>
-      </c>
-      <c r="AK12" s="5">
-        <f t="shared" si="38"/>
-        <v>1317.1714318461611</v>
-      </c>
-      <c r="AL12" s="5">
-        <f t="shared" si="38"/>
-        <v>1419.7115857968972</v>
-      </c>
-      <c r="AM12" s="5">
-        <f t="shared" si="38"/>
-        <v>1478.9385561893014</v>
-      </c>
-      <c r="AN12" s="5">
-        <f t="shared" si="38"/>
-        <v>1543.8634492924632</v>
-      </c>
-      <c r="AO12" s="5">
-        <f t="shared" si="38"/>
-        <v>1611.1159013881586</v>
-      </c>
-      <c r="AP12" s="5">
-        <f t="shared" si="38"/>
-        <v>1680.8015693347879</v>
+      <c r="AW12" s="5">
+        <v>949</v>
+      </c>
+      <c r="AX12" s="5">
+        <v>1211</v>
+      </c>
+      <c r="AY12" s="5">
+        <v>1475</v>
+      </c>
+      <c r="AZ12" s="5">
+        <v>1700</v>
+      </c>
+      <c r="BA12" s="5">
+        <f t="shared" ref="BA12" si="53">BA11*0.22</f>
+        <v>1655.0316639999994</v>
+      </c>
+      <c r="BB12" s="5">
+        <f t="shared" ref="AX12:BF12" si="54">BB11*0.22</f>
+        <v>1653.2345332799994</v>
+      </c>
+      <c r="BC12" s="5">
+        <f t="shared" si="54"/>
+        <v>1713.6857271188148</v>
+      </c>
+      <c r="BD12" s="5">
+        <f t="shared" si="54"/>
+        <v>1792.4816182052248</v>
+      </c>
+      <c r="BE12" s="5">
+        <f t="shared" si="54"/>
+        <v>1874.052674209134</v>
+      </c>
+      <c r="BF12" s="5">
+        <f t="shared" si="54"/>
+        <v>1958.6182312947797</v>
+      </c>
+      <c r="BG12" s="5">
+        <f t="shared" ref="BG12:BK12" si="55">BG11*0.22</f>
+        <v>1988.5548305426933</v>
+      </c>
+      <c r="BH12" s="5">
+        <f t="shared" si="55"/>
+        <v>2019.2527911286345</v>
+      </c>
+      <c r="BI12" s="5">
+        <f t="shared" si="55"/>
+        <v>2050.2779429321472</v>
+      </c>
+      <c r="BJ12" s="5">
+        <f t="shared" si="55"/>
+        <v>2081.6312128805685</v>
+      </c>
+      <c r="BK12" s="5">
+        <f t="shared" si="55"/>
+        <v>2113.309783425791</v>
       </c>
     </row>
-    <row r="13" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:164" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10">
-        <f t="shared" ref="C13:V13" si="39">C11-C12</f>
+      <c r="C13" s="9">
+        <f t="shared" ref="C13:V13" si="56">C11-C12</f>
         <v>556</v>
       </c>
-      <c r="D13" s="10">
-        <f t="shared" si="39"/>
+      <c r="D13" s="9">
+        <f t="shared" si="56"/>
         <v>702</v>
       </c>
-      <c r="E13" s="10">
-        <f t="shared" si="39"/>
+      <c r="E13" s="9">
+        <f t="shared" si="56"/>
         <v>951</v>
       </c>
-      <c r="F13" s="10">
-        <f t="shared" si="39"/>
+      <c r="F13" s="9">
+        <f t="shared" si="56"/>
         <v>953</v>
       </c>
-      <c r="G13" s="10">
-        <f t="shared" si="39"/>
+      <c r="G13" s="9">
+        <f t="shared" si="56"/>
         <v>653</v>
       </c>
-      <c r="H13" s="10">
-        <f t="shared" si="39"/>
+      <c r="H13" s="9">
+        <f t="shared" si="56"/>
         <v>712</v>
       </c>
-      <c r="I13" s="10">
-        <f t="shared" si="39"/>
+      <c r="I13" s="9">
+        <f t="shared" si="56"/>
         <v>978</v>
       </c>
-      <c r="J13" s="10">
-        <f t="shared" si="39"/>
+      <c r="J13" s="9">
+        <f t="shared" si="56"/>
         <v>1029</v>
       </c>
-      <c r="K13" s="10">
-        <f t="shared" si="39"/>
+      <c r="K13" s="9">
+        <f t="shared" si="56"/>
         <v>670</v>
       </c>
-      <c r="L13" s="10">
-        <f t="shared" si="39"/>
+      <c r="L13" s="9">
+        <f t="shared" si="56"/>
         <v>742</v>
       </c>
-      <c r="M13" s="10">
-        <f t="shared" si="39"/>
+      <c r="M13" s="9">
+        <f t="shared" si="56"/>
         <v>1032</v>
       </c>
-      <c r="N13" s="10">
-        <f t="shared" si="39"/>
+      <c r="N13" s="9">
+        <f t="shared" si="56"/>
         <v>1007</v>
       </c>
-      <c r="O13" s="10">
-        <f t="shared" si="39"/>
+      <c r="O13" s="9">
+        <f t="shared" si="56"/>
         <v>736</v>
       </c>
-      <c r="P13" s="10">
-        <f t="shared" si="39"/>
+      <c r="P13" s="9">
+        <f t="shared" si="56"/>
         <v>816</v>
       </c>
-      <c r="Q13" s="10">
-        <f t="shared" si="39"/>
+      <c r="Q13" s="9">
+        <f t="shared" si="56"/>
         <v>1174</v>
       </c>
-      <c r="R13" s="10">
-        <f t="shared" si="39"/>
+      <c r="R13" s="9">
+        <f t="shared" si="56"/>
         <v>921</v>
       </c>
-      <c r="S13" s="10">
-        <f t="shared" si="39"/>
+      <c r="S13" s="9">
+        <f t="shared" si="56"/>
         <v>-414</v>
       </c>
-      <c r="T13" s="10">
-        <f t="shared" si="39"/>
+      <c r="T13" s="9">
+        <f t="shared" si="56"/>
         <v>216</v>
       </c>
-      <c r="U13" s="10">
-        <f t="shared" si="39"/>
+      <c r="U13" s="9">
+        <f t="shared" si="56"/>
         <v>1317</v>
       </c>
-      <c r="V13" s="10">
-        <f t="shared" si="39"/>
+      <c r="V13" s="9">
+        <f t="shared" si="56"/>
         <v>117.01000000000022</v>
       </c>
-      <c r="W13" s="10">
-        <f t="shared" ref="W13:Z13" si="40">W11-W12</f>
+      <c r="W13" s="9">
+        <f t="shared" ref="W13:Z13" si="57">W11-W12</f>
         <v>389.99493000000001</v>
       </c>
-      <c r="X13" s="10">
-        <f t="shared" si="40"/>
+      <c r="X13" s="9">
+        <f t="shared" si="57"/>
         <v>617.09700000000021</v>
       </c>
-      <c r="Y13" s="10">
-        <f t="shared" si="40"/>
+      <c r="Y13" s="9">
+        <f t="shared" si="57"/>
         <v>984.63143999999988</v>
       </c>
-      <c r="Z13" s="10">
-        <f t="shared" si="40"/>
+      <c r="Z13" s="9">
+        <f t="shared" si="57"/>
         <v>455.51313600000032</v>
       </c>
-      <c r="AB13" s="10">
-        <f t="shared" ref="AB13:AF13" si="41">AB11-AB12</f>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9">
+        <f t="shared" ref="AI13:AJ13" si="58">AI11-AI12</f>
+        <v>1298</v>
+      </c>
+      <c r="AJ13" s="9">
+        <f t="shared" si="58"/>
+        <v>1480</v>
+      </c>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="9"/>
+      <c r="AM13" s="9">
+        <f t="shared" ref="AM13:AN13" si="59">AM11-AM12</f>
+        <v>1306</v>
+      </c>
+      <c r="AN13" s="9">
+        <f t="shared" si="59"/>
+        <v>1486</v>
+      </c>
+      <c r="AO13" s="9"/>
+      <c r="AP13" s="9"/>
+      <c r="AR13" s="9">
+        <f t="shared" ref="AR13:AW13" si="60">AR11-AR12</f>
         <v>3162</v>
       </c>
-      <c r="AC13" s="10">
-        <f t="shared" si="41"/>
+      <c r="AS13" s="9">
+        <f t="shared" si="60"/>
         <v>3372</v>
       </c>
-      <c r="AD13" s="10">
-        <f t="shared" si="41"/>
+      <c r="AT13" s="9">
+        <f t="shared" si="60"/>
         <v>3451</v>
       </c>
-      <c r="AE13" s="10">
-        <f t="shared" si="41"/>
+      <c r="AU13" s="9">
+        <f t="shared" si="60"/>
         <v>3647</v>
       </c>
-      <c r="AF13" s="10">
-        <f t="shared" si="41"/>
+      <c r="AV13" s="9">
+        <f t="shared" si="60"/>
         <v>1105</v>
       </c>
-      <c r="AG13" s="10">
-        <f t="shared" ref="AG13" si="42">AG11-AG12</f>
-        <v>2447.236506000002</v>
-      </c>
-      <c r="AH13" s="10">
-        <f t="shared" ref="AH13" si="43">AH11-AH12</f>
-        <v>3288.5182434000017</v>
-      </c>
-      <c r="AI13" s="10">
-        <f t="shared" ref="AI13" si="44">AI11-AI12</f>
-        <v>3964.323403872002</v>
-      </c>
-      <c r="AJ13" s="10">
-        <f t="shared" ref="AJ13" si="45">AJ11-AJ12</f>
-        <v>4307.8303576776052</v>
-      </c>
-      <c r="AK13" s="10">
-        <f t="shared" ref="AK13" si="46">AK11-AK12</f>
-        <v>4669.9714401818446</v>
-      </c>
-      <c r="AL13" s="10">
-        <f t="shared" ref="AL13" si="47">AL11-AL12</f>
-        <v>5033.52289509809</v>
-      </c>
-      <c r="AM13" s="10">
-        <f t="shared" ref="AM13" si="48">AM11-AM12</f>
-        <v>5243.5094264893414</v>
-      </c>
-      <c r="AN13" s="10">
-        <f t="shared" ref="AN13" si="49">AN11-AN12</f>
-        <v>5473.6976838550972</v>
-      </c>
-      <c r="AO13" s="10">
-        <f t="shared" ref="AO13" si="50">AO11-AO12</f>
-        <v>5712.1381958307438</v>
-      </c>
-      <c r="AP13" s="10">
-        <f t="shared" ref="AP13" si="51">AP11-AP12</f>
-        <v>5959.2055640051567</v>
-      </c>
-      <c r="AQ13" s="1">
-        <f>AP13*(1+$AS$19)</f>
-        <v>5899.6135083651052</v>
-      </c>
-      <c r="AR13" s="1">
-        <f t="shared" ref="AR13:DC13" si="52">AQ13*(1+$AS$19)</f>
-        <v>5840.6173732814541</v>
-      </c>
-      <c r="AS13" s="1">
-        <f t="shared" si="52"/>
-        <v>5782.2111995486393</v>
-      </c>
-      <c r="AT13" s="1">
-        <f t="shared" si="52"/>
-        <v>5724.3890875531533</v>
-      </c>
-      <c r="AU13" s="1">
-        <f t="shared" si="52"/>
-        <v>5667.1451966776222</v>
-      </c>
-      <c r="AV13" s="1">
-        <f t="shared" si="52"/>
-        <v>5610.4737447108455</v>
-      </c>
-      <c r="AW13" s="1">
-        <f t="shared" si="52"/>
-        <v>5554.3690072637373</v>
-      </c>
-      <c r="AX13" s="1">
-        <f t="shared" si="52"/>
-        <v>5498.8253171911001</v>
-      </c>
-      <c r="AY13" s="1">
-        <f t="shared" si="52"/>
-        <v>5443.8370640191888</v>
-      </c>
-      <c r="AZ13" s="1">
-        <f t="shared" si="52"/>
-        <v>5389.3986933789965</v>
-      </c>
-      <c r="BA13" s="1">
-        <f t="shared" si="52"/>
-        <v>5335.5047064452065</v>
-      </c>
-      <c r="BB13" s="1">
-        <f t="shared" si="52"/>
-        <v>5282.1496593807542</v>
-      </c>
-      <c r="BC13" s="1">
-        <f t="shared" si="52"/>
-        <v>5229.3281627869465</v>
-      </c>
-      <c r="BD13" s="1">
-        <f t="shared" si="52"/>
-        <v>5177.0348811590766</v>
-      </c>
-      <c r="BE13" s="1">
-        <f t="shared" si="52"/>
-        <v>5125.2645323474853</v>
-      </c>
-      <c r="BF13" s="1">
-        <f t="shared" si="52"/>
-        <v>5074.0118870240103</v>
-      </c>
-      <c r="BG13" s="1">
-        <f t="shared" si="52"/>
-        <v>5023.2717681537706</v>
-      </c>
-      <c r="BH13" s="1">
-        <f t="shared" si="52"/>
-        <v>4973.0390504722327</v>
-      </c>
-      <c r="BI13" s="1">
-        <f t="shared" si="52"/>
-        <v>4923.3086599675107</v>
-      </c>
-      <c r="BJ13" s="1">
-        <f t="shared" si="52"/>
-        <v>4874.0755733678352</v>
-      </c>
-      <c r="BK13" s="1">
-        <f t="shared" si="52"/>
-        <v>4825.3348176341569</v>
+      <c r="AW13" s="9">
+        <f t="shared" si="60"/>
+        <v>3249</v>
+      </c>
+      <c r="AX13" s="9">
+        <f t="shared" ref="AX13:AZ13" si="61">AX11-AX12</f>
+        <v>4146</v>
+      </c>
+      <c r="AY13" s="9">
+        <f t="shared" si="61"/>
+        <v>5394</v>
+      </c>
+      <c r="AZ13" s="9">
+        <f t="shared" si="61"/>
+        <v>5877</v>
+      </c>
+      <c r="BA13" s="9">
+        <f t="shared" ref="BA13:BB13" si="62">BA11-BA12</f>
+        <v>5867.8395359999977</v>
+      </c>
+      <c r="BB13" s="9">
+        <f t="shared" si="62"/>
+        <v>5861.4678907199977</v>
+      </c>
+      <c r="BC13" s="9">
+        <f t="shared" ref="BC13" si="63">BC11-BC12</f>
+        <v>6075.7948506939802</v>
+      </c>
+      <c r="BD13" s="9">
+        <f t="shared" ref="BD13" si="64">BD11-BD12</f>
+        <v>6355.1621009094333</v>
+      </c>
+      <c r="BE13" s="9">
+        <f t="shared" ref="BE13" si="65">BE11-BE12</f>
+        <v>6644.3685721960201</v>
+      </c>
+      <c r="BF13" s="9">
+        <f t="shared" ref="BF13:BK13" si="66">BF11-BF12</f>
+        <v>6944.1919109542187</v>
+      </c>
+      <c r="BG13" s="9">
+        <f t="shared" si="66"/>
+        <v>7050.3307628331859</v>
+      </c>
+      <c r="BH13" s="9">
+        <f t="shared" si="66"/>
+        <v>7159.1689867287951</v>
+      </c>
+      <c r="BI13" s="9">
+        <f t="shared" si="66"/>
+        <v>7269.1672522139761</v>
+      </c>
+      <c r="BJ13" s="9">
+        <f t="shared" si="66"/>
+        <v>7380.32884566747</v>
+      </c>
+      <c r="BK13" s="9">
+        <f t="shared" si="66"/>
+        <v>7492.6437776005314</v>
       </c>
       <c r="BL13" s="1">
-        <f t="shared" si="52"/>
-        <v>4777.0814694578157</v>
+        <f>BK13*(1+$BN$19)</f>
+        <v>7417.7173398245259</v>
       </c>
       <c r="BM13" s="1">
-        <f t="shared" si="52"/>
-        <v>4729.3106547632378</v>
+        <f t="shared" ref="BM13:DX13" si="67">BL13*(1+$BN$19)</f>
+        <v>7343.5401664262808</v>
       </c>
       <c r="BN13" s="1">
-        <f t="shared" si="52"/>
-        <v>4682.0175482156055</v>
+        <f t="shared" si="67"/>
+        <v>7270.104764762018</v>
       </c>
       <c r="BO13" s="1">
-        <f t="shared" si="52"/>
-        <v>4635.1973727334498</v>
+        <f t="shared" si="67"/>
+        <v>7197.4037171143982</v>
       </c>
       <c r="BP13" s="1">
-        <f t="shared" si="52"/>
-        <v>4588.8453990061153</v>
+        <f t="shared" si="67"/>
+        <v>7125.4296799432541</v>
       </c>
       <c r="BQ13" s="1">
-        <f t="shared" si="52"/>
-        <v>4542.9569450160543</v>
+        <f t="shared" si="67"/>
+        <v>7054.1753831438218</v>
       </c>
       <c r="BR13" s="1">
-        <f t="shared" si="52"/>
-        <v>4497.5273755658936</v>
+        <f t="shared" si="67"/>
+        <v>6983.6336293123832</v>
       </c>
       <c r="BS13" s="1">
-        <f t="shared" si="52"/>
-        <v>4452.5521018102345</v>
+        <f t="shared" si="67"/>
+        <v>6913.7972930192591</v>
       </c>
       <c r="BT13" s="1">
-        <f t="shared" si="52"/>
-        <v>4408.0265807921323</v>
+        <f t="shared" si="67"/>
+        <v>6844.6593200890666</v>
       </c>
       <c r="BU13" s="1">
-        <f t="shared" si="52"/>
-        <v>4363.9463149842113</v>
+        <f t="shared" si="67"/>
+        <v>6776.2127268881759</v>
       </c>
       <c r="BV13" s="1">
-        <f t="shared" si="52"/>
-        <v>4320.3068518343689</v>
+        <f t="shared" si="67"/>
+        <v>6708.4505996192938</v>
       </c>
       <c r="BW13" s="1">
-        <f t="shared" si="52"/>
-        <v>4277.1037833160253</v>
+        <f t="shared" si="67"/>
+        <v>6641.3660936231008</v>
       </c>
       <c r="BX13" s="1">
-        <f t="shared" si="52"/>
-        <v>4234.332745482865</v>
+        <f t="shared" si="67"/>
+        <v>6574.9524326868695</v>
       </c>
       <c r="BY13" s="1">
-        <f t="shared" si="52"/>
-        <v>4191.9894180280362</v>
+        <f t="shared" si="67"/>
+        <v>6509.2029083600009</v>
       </c>
       <c r="BZ13" s="1">
-        <f t="shared" si="52"/>
-        <v>4150.0695238477556</v>
+        <f t="shared" si="67"/>
+        <v>6444.1108792764007</v>
       </c>
       <c r="CA13" s="1">
-        <f t="shared" si="52"/>
-        <v>4108.5688286092782</v>
+        <f t="shared" si="67"/>
+        <v>6379.669770483637</v>
       </c>
       <c r="CB13" s="1">
-        <f t="shared" si="52"/>
-        <v>4067.4831403231851</v>
+        <f t="shared" si="67"/>
+        <v>6315.8730727788006</v>
       </c>
       <c r="CC13" s="1">
-        <f t="shared" si="52"/>
-        <v>4026.8083089199531</v>
+        <f t="shared" si="67"/>
+        <v>6252.7143420510129</v>
       </c>
       <c r="CD13" s="1">
-        <f t="shared" si="52"/>
-        <v>3986.5402258307536</v>
+        <f t="shared" si="67"/>
+        <v>6190.1871986305023</v>
       </c>
       <c r="CE13" s="1">
-        <f t="shared" si="52"/>
-        <v>3946.6748235724458</v>
+        <f t="shared" si="67"/>
+        <v>6128.2853266441971</v>
       </c>
       <c r="CF13" s="1">
-        <f t="shared" si="52"/>
-        <v>3907.2080753367213</v>
+        <f t="shared" si="67"/>
+        <v>6067.0024733777555</v>
       </c>
       <c r="CG13" s="1">
-        <f t="shared" si="52"/>
-        <v>3868.1359945833542</v>
+        <f t="shared" si="67"/>
+        <v>6006.3324486439778</v>
       </c>
       <c r="CH13" s="1">
-        <f t="shared" si="52"/>
-        <v>3829.4546346375205</v>
+        <f t="shared" si="67"/>
+        <v>5946.2691241575376</v>
       </c>
       <c r="CI13" s="1">
-        <f t="shared" si="52"/>
-        <v>3791.1600882911453</v>
+        <f t="shared" si="67"/>
+        <v>5886.8064329159624</v>
       </c>
       <c r="CJ13" s="1">
-        <f t="shared" si="52"/>
-        <v>3753.2484874082338</v>
+        <f t="shared" si="67"/>
+        <v>5827.9383685868024</v>
       </c>
       <c r="CK13" s="1">
-        <f t="shared" si="52"/>
-        <v>3715.7160025341514</v>
+        <f t="shared" si="67"/>
+        <v>5769.6589849009342</v>
       </c>
       <c r="CL13" s="1">
-        <f t="shared" si="52"/>
-        <v>3678.5588425088099</v>
+        <f t="shared" si="67"/>
+        <v>5711.9623950519244</v>
       </c>
       <c r="CM13" s="1">
-        <f t="shared" si="52"/>
-        <v>3641.7732540837219</v>
+        <f t="shared" si="67"/>
+        <v>5654.8427711014056</v>
       </c>
       <c r="CN13" s="1">
-        <f t="shared" si="52"/>
-        <v>3605.3555215428846</v>
+        <f t="shared" si="67"/>
+        <v>5598.2943433903911</v>
       </c>
       <c r="CO13" s="1">
-        <f t="shared" si="52"/>
-        <v>3569.3019663274558</v>
+        <f t="shared" si="67"/>
+        <v>5542.3113999564875</v>
       </c>
       <c r="CP13" s="1">
-        <f t="shared" si="52"/>
-        <v>3533.6089466641811</v>
+        <f t="shared" si="67"/>
+        <v>5486.888285956923</v>
       </c>
       <c r="CQ13" s="1">
-        <f t="shared" si="52"/>
-        <v>3498.2728571975395</v>
+        <f t="shared" si="67"/>
+        <v>5432.0194030973535</v>
       </c>
       <c r="CR13" s="1">
-        <f t="shared" si="52"/>
-        <v>3463.2901286255642</v>
+        <f t="shared" si="67"/>
+        <v>5377.6992090663798</v>
       </c>
       <c r="CS13" s="1">
-        <f t="shared" si="52"/>
-        <v>3428.6572273393085</v>
+        <f t="shared" si="67"/>
+        <v>5323.9222169757159</v>
       </c>
       <c r="CT13" s="1">
-        <f t="shared" si="52"/>
-        <v>3394.3706550659153</v>
+        <f t="shared" si="67"/>
+        <v>5270.6829948059585</v>
       </c>
       <c r="CU13" s="1">
-        <f t="shared" si="52"/>
-        <v>3360.4269485152563</v>
+        <f t="shared" si="67"/>
+        <v>5217.9761648578988</v>
       </c>
       <c r="CV13" s="1">
-        <f t="shared" si="52"/>
-        <v>3326.8226790301037</v>
+        <f t="shared" si="67"/>
+        <v>5165.7964032093196</v>
       </c>
       <c r="CW13" s="1">
-        <f t="shared" si="52"/>
-        <v>3293.5544522398027</v>
+        <f t="shared" si="67"/>
+        <v>5114.1384391772262</v>
       </c>
       <c r="CX13" s="1">
-        <f t="shared" si="52"/>
-        <v>3260.6189077174045</v>
+        <f t="shared" si="67"/>
+        <v>5062.9970547854537</v>
       </c>
       <c r="CY13" s="1">
-        <f t="shared" si="52"/>
-        <v>3228.0127186402306</v>
+        <f t="shared" si="67"/>
+        <v>5012.3670842375986</v>
       </c>
       <c r="CZ13" s="1">
-        <f t="shared" si="52"/>
-        <v>3195.7325914538283</v>
+        <f t="shared" si="67"/>
+        <v>4962.2434133952229</v>
       </c>
       <c r="DA13" s="1">
-        <f t="shared" si="52"/>
-        <v>3163.7752655392901</v>
+        <f t="shared" si="67"/>
+        <v>4912.6209792612708</v>
       </c>
       <c r="DB13" s="1">
-        <f t="shared" si="52"/>
-        <v>3132.1375128838972</v>
+        <f t="shared" si="67"/>
+        <v>4863.494769468658</v>
       </c>
       <c r="DC13" s="1">
-        <f t="shared" si="52"/>
-        <v>3100.8161377550582</v>
+        <f t="shared" si="67"/>
+        <v>4814.8598217739709</v>
       </c>
       <c r="DD13" s="1">
-        <f t="shared" ref="DD13:EM13" si="53">DC13*(1+$AS$19)</f>
-        <v>3069.8079763775077</v>
+        <f t="shared" si="67"/>
+        <v>4766.7112235562308</v>
       </c>
       <c r="DE13" s="1">
-        <f t="shared" si="53"/>
-        <v>3039.1098966137324</v>
+        <f t="shared" si="67"/>
+        <v>4719.0441113206689</v>
       </c>
       <c r="DF13" s="1">
-        <f t="shared" si="53"/>
-        <v>3008.7187976475952</v>
+        <f t="shared" si="67"/>
+        <v>4671.8536702074625</v>
       </c>
       <c r="DG13" s="1">
-        <f t="shared" si="53"/>
-        <v>2978.6316096711193</v>
+        <f t="shared" si="67"/>
+        <v>4625.1351335053878</v>
       </c>
       <c r="DH13" s="1">
-        <f t="shared" si="53"/>
-        <v>2948.8452935744081</v>
+        <f t="shared" si="67"/>
+        <v>4578.8837821703337</v>
       </c>
       <c r="DI13" s="1">
-        <f t="shared" si="53"/>
-        <v>2919.3568406386639</v>
+        <f t="shared" si="67"/>
+        <v>4533.0949443486306</v>
       </c>
       <c r="DJ13" s="1">
-        <f t="shared" si="53"/>
-        <v>2890.1632722322774</v>
+        <f t="shared" si="67"/>
+        <v>4487.7639949051445</v>
       </c>
       <c r="DK13" s="1">
-        <f t="shared" si="53"/>
-        <v>2861.2616395099549</v>
+        <f t="shared" si="67"/>
+        <v>4442.8863549560929</v>
       </c>
       <c r="DL13" s="1">
-        <f t="shared" si="53"/>
-        <v>2832.6490231148555</v>
+        <f t="shared" si="67"/>
+        <v>4398.4574914065315</v>
       </c>
       <c r="DM13" s="1">
-        <f t="shared" si="53"/>
-        <v>2804.322532883707</v>
+        <f t="shared" si="67"/>
+        <v>4354.4729164924665</v>
       </c>
       <c r="DN13" s="1">
-        <f t="shared" si="53"/>
-        <v>2776.2793075548698</v>
+        <f t="shared" si="67"/>
+        <v>4310.9281873275422</v>
       </c>
       <c r="DO13" s="1">
-        <f t="shared" si="53"/>
-        <v>2748.5165144793209</v>
+        <f t="shared" si="67"/>
+        <v>4267.8189054542663</v>
       </c>
       <c r="DP13" s="1">
-        <f t="shared" si="53"/>
-        <v>2721.0313493345275</v>
+        <f t="shared" si="67"/>
+        <v>4225.1407163997237</v>
       </c>
       <c r="DQ13" s="1">
-        <f t="shared" si="53"/>
-        <v>2693.821035841182</v>
+        <f t="shared" si="67"/>
+        <v>4182.8893092357266</v>
       </c>
       <c r="DR13" s="1">
-        <f t="shared" si="53"/>
-        <v>2666.8828254827704</v>
+        <f t="shared" si="67"/>
+        <v>4141.0604161433694</v>
       </c>
       <c r="DS13" s="1">
-        <f t="shared" si="53"/>
-        <v>2640.2139972279429</v>
+        <f t="shared" si="67"/>
+        <v>4099.6498119819353</v>
       </c>
       <c r="DT13" s="1">
-        <f t="shared" si="53"/>
-        <v>2613.8118572556632</v>
+        <f t="shared" si="67"/>
+        <v>4058.6533138621157</v>
       </c>
       <c r="DU13" s="1">
-        <f t="shared" si="53"/>
-        <v>2587.6737386831064</v>
+        <f t="shared" si="67"/>
+        <v>4018.0667807234945</v>
       </c>
       <c r="DV13" s="1">
-        <f t="shared" si="53"/>
-        <v>2561.7970012962755</v>
+        <f t="shared" si="67"/>
+        <v>3977.8861129162597</v>
       </c>
       <c r="DW13" s="1">
-        <f t="shared" si="53"/>
-        <v>2536.1790312833127</v>
+        <f t="shared" si="67"/>
+        <v>3938.1072517870971</v>
       </c>
       <c r="DX13" s="1">
-        <f t="shared" si="53"/>
-        <v>2510.8172409704794</v>
+        <f t="shared" si="67"/>
+        <v>3898.7261792692261</v>
       </c>
       <c r="DY13" s="1">
-        <f t="shared" si="53"/>
-        <v>2485.7090685607745</v>
+        <f t="shared" ref="DY13:FH13" si="68">DX13*(1+$BN$19)</f>
+        <v>3859.738917476534</v>
       </c>
       <c r="DZ13" s="1">
-        <f t="shared" si="53"/>
-        <v>2460.851977875167</v>
+        <f t="shared" si="68"/>
+        <v>3821.1415283017686</v>
       </c>
       <c r="EA13" s="1">
-        <f t="shared" si="53"/>
-        <v>2436.2434580964155</v>
+        <f t="shared" si="68"/>
+        <v>3782.9301130187509</v>
       </c>
       <c r="EB13" s="1">
-        <f t="shared" si="53"/>
-        <v>2411.8810235154515</v>
+        <f t="shared" si="68"/>
+        <v>3745.1008118885634</v>
       </c>
       <c r="EC13" s="1">
-        <f t="shared" si="53"/>
-        <v>2387.7622132802971</v>
+        <f t="shared" si="68"/>
+        <v>3707.6498037696779</v>
       </c>
       <c r="ED13" s="1">
-        <f t="shared" si="53"/>
-        <v>2363.8845911474941</v>
+        <f t="shared" si="68"/>
+        <v>3670.5733057319812</v>
       </c>
       <c r="EE13" s="1">
-        <f t="shared" si="53"/>
-        <v>2340.245745236019</v>
+        <f t="shared" si="68"/>
+        <v>3633.8675726746615</v>
       </c>
       <c r="EF13" s="1">
-        <f t="shared" si="53"/>
-        <v>2316.843287783659</v>
+        <f t="shared" si="68"/>
+        <v>3597.5288969479147</v>
       </c>
       <c r="EG13" s="1">
-        <f t="shared" si="53"/>
-        <v>2293.6748549058225</v>
+        <f t="shared" si="68"/>
+        <v>3561.5536079784356</v>
       </c>
       <c r="EH13" s="1">
-        <f t="shared" si="53"/>
-        <v>2270.7381063567641</v>
+        <f t="shared" si="68"/>
+        <v>3525.9380718986513</v>
       </c>
       <c r="EI13" s="1">
-        <f t="shared" si="53"/>
-        <v>2248.0307252931966</v>
+        <f t="shared" si="68"/>
+        <v>3490.6786911796648</v>
       </c>
       <c r="EJ13" s="1">
-        <f t="shared" si="53"/>
-        <v>2225.5504180402645</v>
+        <f t="shared" si="68"/>
+        <v>3455.7719042678682</v>
       </c>
       <c r="EK13" s="1">
-        <f t="shared" si="53"/>
-        <v>2203.2949138598619</v>
+        <f t="shared" si="68"/>
+        <v>3421.2141852251893</v>
       </c>
       <c r="EL13" s="1">
-        <f t="shared" si="53"/>
-        <v>2181.2619647212632</v>
+        <f t="shared" si="68"/>
+        <v>3387.0020433729374</v>
       </c>
       <c r="EM13" s="1">
-        <f t="shared" si="53"/>
-        <v>2159.4493450740506</v>
+        <f t="shared" si="68"/>
+        <v>3353.1320229392081</v>
+      </c>
+      <c r="EN13" s="1">
+        <f t="shared" si="68"/>
+        <v>3319.6007027098162</v>
+      </c>
+      <c r="EO13" s="1">
+        <f t="shared" si="68"/>
+        <v>3286.4046956827178</v>
+      </c>
+      <c r="EP13" s="1">
+        <f t="shared" si="68"/>
+        <v>3253.5406487258906</v>
+      </c>
+      <c r="EQ13" s="1">
+        <f t="shared" si="68"/>
+        <v>3221.0052422386316</v>
+      </c>
+      <c r="ER13" s="1">
+        <f t="shared" si="68"/>
+        <v>3188.7951898162451</v>
+      </c>
+      <c r="ES13" s="1">
+        <f t="shared" si="68"/>
+        <v>3156.9072379180825</v>
+      </c>
+      <c r="ET13" s="1">
+        <f t="shared" si="68"/>
+        <v>3125.3381655389016</v>
+      </c>
+      <c r="EU13" s="1">
+        <f t="shared" si="68"/>
+        <v>3094.0847838835125</v>
+      </c>
+      <c r="EV13" s="1">
+        <f t="shared" si="68"/>
+        <v>3063.1439360446775</v>
+      </c>
+      <c r="EW13" s="1">
+        <f t="shared" si="68"/>
+        <v>3032.5124966842309</v>
+      </c>
+      <c r="EX13" s="1">
+        <f t="shared" si="68"/>
+        <v>3002.1873717173885</v>
+      </c>
+      <c r="EY13" s="1">
+        <f t="shared" si="68"/>
+        <v>2972.1654980002145</v>
+      </c>
+      <c r="EZ13" s="1">
+        <f t="shared" si="68"/>
+        <v>2942.4438430202122</v>
+      </c>
+      <c r="FA13" s="1">
+        <f t="shared" si="68"/>
+        <v>2913.0194045900098</v>
+      </c>
+      <c r="FB13" s="1">
+        <f t="shared" si="68"/>
+        <v>2883.8892105441096</v>
+      </c>
+      <c r="FC13" s="1">
+        <f t="shared" si="68"/>
+        <v>2855.0503184386685</v>
+      </c>
+      <c r="FD13" s="1">
+        <f t="shared" si="68"/>
+        <v>2826.4998152542817</v>
+      </c>
+      <c r="FE13" s="1">
+        <f t="shared" si="68"/>
+        <v>2798.2348171017388</v>
+      </c>
+      <c r="FF13" s="1">
+        <f t="shared" si="68"/>
+        <v>2770.2524689307215</v>
+      </c>
+      <c r="FG13" s="1">
+        <f t="shared" si="68"/>
+        <v>2742.5499442414143</v>
+      </c>
+      <c r="FH13" s="1">
+        <f t="shared" si="68"/>
+        <v>2715.1244447990002</v>
       </c>
     </row>
-    <row r="14" spans="2:143" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:164" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>2</v>
       </c>
@@ -3148,1048 +3865,1688 @@
       <c r="Z14" s="5">
         <v>3115</v>
       </c>
-      <c r="AB14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AC14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AD14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AE14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AF14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AG14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AH14" s="5">
-        <v>3115</v>
-      </c>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AH14" s="5"/>
       <c r="AI14" s="5">
         <v>3115</v>
       </c>
       <c r="AJ14" s="5">
         <v>3115</v>
       </c>
-      <c r="AK14" s="5">
-        <v>3115</v>
-      </c>
-      <c r="AL14" s="5">
-        <v>3115</v>
-      </c>
+      <c r="AK14" s="5"/>
+      <c r="AL14" s="5"/>
       <c r="AM14" s="5">
         <v>3115</v>
       </c>
       <c r="AN14" s="5">
         <v>3115</v>
       </c>
-      <c r="AO14" s="5">
+      <c r="AO14" s="5"/>
+      <c r="AP14" s="5"/>
+      <c r="AR14" s="5">
         <v>3115</v>
       </c>
-      <c r="AP14" s="5">
+      <c r="AS14" s="5">
         <v>3115</v>
       </c>
+      <c r="AT14" s="5">
+        <v>3115</v>
+      </c>
+      <c r="AU14" s="5">
+        <v>3115</v>
+      </c>
+      <c r="AV14" s="5">
+        <v>3115</v>
+      </c>
+      <c r="AW14" s="5">
+        <v>3115</v>
+      </c>
+      <c r="AX14" s="5">
+        <v>3115</v>
+      </c>
+      <c r="AY14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="AZ14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BA14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BB14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BC14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BD14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BE14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BF14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BG14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BH14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BI14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BJ14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
+      <c r="BK14" s="5">
+        <f>3115.8</f>
+        <v>3115.8</v>
+      </c>
     </row>
-    <row r="15" spans="2:143" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:164" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:V15" si="54">C13/C14</f>
+        <f t="shared" ref="C15:V15" si="69">C13/C14</f>
         <v>0.17849117174959872</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.22536115569823434</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.30529695024077047</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.30593900481540931</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.20963081861958266</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.22857142857142856</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.31396468699839486</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.33033707865168538</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.21508828250401285</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.23820224719101124</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.33130016051364364</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.32327447833065809</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.23627608346709469</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.26195826645264847</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.37688603531300163</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.29566613162118782</v>
       </c>
       <c r="S15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>-0.13290529695024078</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>6.9341894060995182E-2</v>
       </c>
       <c r="U15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>0.42279293739967899</v>
       </c>
       <c r="V15" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>3.7563402889245659E-2</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" ref="W15:Z15" si="55">W13/W14</f>
+        <f t="shared" ref="W15:Z15" si="70">W13/W14</f>
         <v>0.12519901444622794</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="70"/>
         <v>0.19810497592295351</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" si="55"/>
-        <v>0.31609356019261636</v>
+        <f t="shared" si="70"/>
+        <v>0.31609356019261631</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="70"/>
         <v>0.14623214638844312</v>
       </c>
-      <c r="AB15" s="7">
-        <f t="shared" ref="AB15:AF15" si="56">AB13/AB14</f>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7">
+        <f t="shared" ref="AI15:AJ15" si="71">AI13/AI14</f>
+        <v>0.41669341894060996</v>
+      </c>
+      <c r="AJ15" s="7">
+        <f t="shared" si="71"/>
+        <v>0.4751203852327448</v>
+      </c>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="7">
+        <f t="shared" ref="AM15:AN15" si="72">AM13/AM14</f>
+        <v>0.41926163723916532</v>
+      </c>
+      <c r="AN15" s="7">
+        <f t="shared" si="72"/>
+        <v>0.47704654895666132</v>
+      </c>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AR15" s="7">
+        <f t="shared" ref="AR15:AW15" si="73">AR13/AR14</f>
         <v>1.0150882825040128</v>
       </c>
-      <c r="AC15" s="7">
-        <f t="shared" si="56"/>
+      <c r="AS15" s="7">
+        <f t="shared" si="73"/>
         <v>1.0825040128410914</v>
       </c>
-      <c r="AD15" s="7">
-        <f t="shared" si="56"/>
+      <c r="AT15" s="7">
+        <f t="shared" si="73"/>
         <v>1.1078651685393259</v>
       </c>
-      <c r="AE15" s="7">
-        <f t="shared" si="56"/>
+      <c r="AU15" s="7">
+        <f t="shared" si="73"/>
         <v>1.1707865168539326</v>
       </c>
-      <c r="AF15" s="7">
-        <f t="shared" si="56"/>
+      <c r="AV15" s="7">
+        <f t="shared" si="73"/>
         <v>0.3547351524879615</v>
       </c>
-      <c r="AG15" s="7">
-        <f t="shared" ref="AG15" si="57">AG13/AG14</f>
-        <v>0.78562969695024143</v>
-      </c>
-      <c r="AH15" s="7">
-        <f t="shared" ref="AH15" si="58">AH13/AH14</f>
-        <v>1.0557040909791338</v>
-      </c>
-      <c r="AI15" s="7">
-        <f t="shared" ref="AI15" si="59">AI13/AI14</f>
-        <v>1.2726559884019268</v>
-      </c>
-      <c r="AJ15" s="7">
-        <f t="shared" ref="AJ15" si="60">AJ13/AJ14</f>
-        <v>1.3829310939574977</v>
-      </c>
-      <c r="AK15" s="7">
-        <f t="shared" ref="AK15" si="61">AK13/AK14</f>
-        <v>1.4991882633007527</v>
-      </c>
-      <c r="AL15" s="7">
-        <f t="shared" ref="AL15" si="62">AL13/AL14</f>
-        <v>1.6158982006735441</v>
-      </c>
-      <c r="AM15" s="7">
-        <f t="shared" ref="AM15" si="63">AM13/AM14</f>
-        <v>1.6833096072196922</v>
-      </c>
-      <c r="AN15" s="7">
-        <f t="shared" ref="AN15" si="64">AN13/AN14</f>
-        <v>1.7572063190546059</v>
-      </c>
-      <c r="AO15" s="7">
-        <f t="shared" ref="AO15" si="65">AO13/AO14</f>
-        <v>1.8337522298012019</v>
-      </c>
-      <c r="AP15" s="7">
-        <f t="shared" ref="AP15" si="66">AP13/AP14</f>
-        <v>1.9130675967913826</v>
+      <c r="AW15" s="7">
+        <f t="shared" si="73"/>
+        <v>1.0430176565008025</v>
+      </c>
+      <c r="AX15" s="7">
+        <f t="shared" ref="AX15:AZ15" si="74">AX13/AX14</f>
+        <v>1.3309791332263243</v>
+      </c>
+      <c r="AY15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.7311765838628923</v>
+      </c>
+      <c r="AZ15" s="7">
+        <f t="shared" si="74"/>
+        <v>1.8861929520508376</v>
+      </c>
+      <c r="BA15" s="7">
+        <f t="shared" ref="BA15:BB15" si="75">BA13/BA14</f>
+        <v>1.8832529481994984</v>
+      </c>
+      <c r="BB15" s="7">
+        <f t="shared" si="75"/>
+        <v>1.8812080013864809</v>
+      </c>
+      <c r="BC15" s="7">
+        <f t="shared" ref="BC15" si="76">BC13/BC14</f>
+        <v>1.9499951379080749</v>
+      </c>
+      <c r="BD15" s="7">
+        <f t="shared" ref="BD15" si="77">BD13/BD14</f>
+        <v>2.0396566213843741</v>
+      </c>
+      <c r="BE15" s="7">
+        <f t="shared" ref="BE15" si="78">BE13/BE14</f>
+        <v>2.1324759523063159</v>
+      </c>
+      <c r="BF15" s="7">
+        <f t="shared" ref="BF15:BK15" si="79">BF13/BF14</f>
+        <v>2.2287027122903327</v>
+      </c>
+      <c r="BG15" s="7">
+        <f t="shared" si="79"/>
+        <v>2.2627674314247339</v>
+      </c>
+      <c r="BH15" s="7">
+        <f t="shared" si="79"/>
+        <v>2.2976985001376193</v>
+      </c>
+      <c r="BI15" s="7">
+        <f t="shared" si="79"/>
+        <v>2.3330018782380049</v>
+      </c>
+      <c r="BJ15" s="7">
+        <f t="shared" si="79"/>
+        <v>2.3686786204722607</v>
+      </c>
+      <c r="BK15" s="7">
+        <f t="shared" si="79"/>
+        <v>2.4047255207653029</v>
       </c>
     </row>
-    <row r="17" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:66" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <f>G3/C3-1</f>
         <v>0.14142242262758753</v>
       </c>
-      <c r="H17" s="9">
-        <f t="shared" ref="H17:V17" si="67">H3/D3-1</f>
+      <c r="H17" s="8">
+        <f t="shared" ref="H17:V17" si="80">H3/D3-1</f>
         <v>9.2373791621911838E-2</v>
       </c>
-      <c r="I17" s="9">
-        <f t="shared" si="67"/>
+      <c r="I17" s="8">
+        <f t="shared" si="80"/>
         <v>5.9626073774633692E-2</v>
       </c>
-      <c r="J17" s="9">
-        <f t="shared" si="67"/>
+      <c r="J17" s="8">
+        <f t="shared" si="80"/>
         <v>6.7313259988419194E-2</v>
       </c>
-      <c r="K17" s="9">
-        <f t="shared" si="67"/>
+      <c r="K17" s="8">
+        <f t="shared" si="80"/>
         <v>1.5263063386604436E-2</v>
       </c>
-      <c r="L17" s="9">
-        <f t="shared" si="67"/>
+      <c r="L17" s="8">
+        <f t="shared" si="80"/>
         <v>4.4247787610619538E-2</v>
       </c>
-      <c r="M17" s="9">
-        <f t="shared" si="67"/>
+      <c r="M17" s="8">
+        <f t="shared" si="80"/>
         <v>1.923382610077895E-2</v>
       </c>
-      <c r="N17" s="9">
-        <f t="shared" si="67"/>
+      <c r="N17" s="8">
+        <f t="shared" si="80"/>
         <v>4.5436050454360499E-2</v>
       </c>
-      <c r="O17" s="9">
-        <f t="shared" si="67"/>
+      <c r="O17" s="8">
+        <f t="shared" si="80"/>
         <v>4.8284400424478235E-2</v>
       </c>
-      <c r="P17" s="9">
-        <f t="shared" si="67"/>
+      <c r="P17" s="8">
+        <f t="shared" si="80"/>
         <v>8.1763967357187717E-2</v>
       </c>
-      <c r="Q17" s="9">
-        <f t="shared" si="67"/>
+      <c r="Q17" s="8">
+        <f t="shared" si="80"/>
         <v>9.1703056768559055E-2</v>
       </c>
-      <c r="R17" s="9">
-        <f t="shared" si="67"/>
+      <c r="R17" s="8">
+        <f t="shared" si="80"/>
         <v>9.8339387649195587E-2</v>
       </c>
-      <c r="S17" s="9">
-        <f t="shared" si="67"/>
+      <c r="S17" s="8">
+        <f t="shared" si="80"/>
         <v>-0.44271975704403577</v>
       </c>
-      <c r="T17" s="9">
-        <f t="shared" si="67"/>
+      <c r="T17" s="8">
+        <f t="shared" si="80"/>
         <v>-0.31379660525170461</v>
       </c>
-      <c r="U17" s="9">
-        <f t="shared" si="67"/>
+      <c r="U17" s="8">
+        <f t="shared" si="80"/>
         <v>-0.13542857142857145</v>
       </c>
-      <c r="V17" s="9">
-        <f t="shared" si="67"/>
+      <c r="V17" s="8">
+        <f t="shared" si="80"/>
         <v>-0.25383888495157103</v>
       </c>
-      <c r="W17" s="9">
-        <f t="shared" ref="W17" si="68">W3/S3-1</f>
+      <c r="W17" s="8">
+        <f t="shared" ref="W17" si="81">W3/S3-1</f>
         <v>0.55000000000000027</v>
       </c>
-      <c r="X17" s="9">
-        <f t="shared" ref="X17" si="69">X3/T3-1</f>
+      <c r="X17" s="8">
+        <f t="shared" ref="X17" si="82">X3/T3-1</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="Y17" s="9">
-        <f t="shared" ref="Y17" si="70">Y3/U3-1</f>
+      <c r="Y17" s="8">
+        <f t="shared" ref="Y17" si="83">Y3/U3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="Z17" s="9">
-        <f t="shared" ref="Z17" si="71">Z3/V3-1</f>
+      <c r="Z17" s="8">
+        <f t="shared" ref="Z17" si="84">Z3/V3-1</f>
         <v>0.12000000000000011</v>
       </c>
-      <c r="AC17" s="9">
-        <f>AC3/AB3-1</f>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8">
+        <f t="shared" ref="AM17:AN17" si="85">AM3/AI3-1</f>
+        <v>1.5214723926380458E-2</v>
+      </c>
+      <c r="AN17" s="8">
+        <f t="shared" si="85"/>
+        <v>1.6944024205748809E-2</v>
+      </c>
+      <c r="AO17" s="8"/>
+      <c r="AP17" s="8"/>
+      <c r="AS17" s="8">
+        <f>AS3/AR3-1</f>
         <v>8.687258687258681E-2</v>
       </c>
-      <c r="AD17" s="9">
-        <f t="shared" ref="AD17:AP17" si="72">AD3/AC3-1</f>
+      <c r="AT17" s="8">
+        <f t="shared" ref="AT17:BF17" si="86">AT3/AS3-1</f>
         <v>3.2011051904480059E-2</v>
       </c>
-      <c r="AE17" s="9">
-        <f t="shared" si="72"/>
+      <c r="AU17" s="8">
+        <f t="shared" si="86"/>
         <v>8.1848083836915775E-2</v>
       </c>
-      <c r="AF17" s="9">
-        <f t="shared" si="72"/>
+      <c r="AV17" s="8">
+        <f t="shared" si="86"/>
         <v>-0.27872445732871387</v>
       </c>
-      <c r="AG17" s="9">
-        <f t="shared" si="72"/>
-        <v>0.22541368493284986</v>
-      </c>
-      <c r="AH17" s="9">
-        <f t="shared" si="72"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AI17" s="9">
-        <f t="shared" si="72"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AJ17" s="9">
-        <f t="shared" si="72"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AK17" s="9">
-        <f t="shared" si="72"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AL17" s="9">
-        <f t="shared" si="72"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AM17" s="9">
-        <f t="shared" si="72"/>
+      <c r="AW17" s="8">
+        <f t="shared" si="86"/>
+        <v>0.3584942652681109</v>
+      </c>
+      <c r="AX17" s="8">
+        <f t="shared" si="86"/>
+        <v>0.17509741665463996</v>
+      </c>
+      <c r="AY17" s="8">
+        <f t="shared" si="86"/>
+        <v>0.10371825969480186</v>
+      </c>
+      <c r="AZ17" s="8">
+        <f t="shared" si="86"/>
+        <v>7.4693298467187752E-2</v>
+      </c>
+      <c r="BA17" s="8">
+        <f t="shared" si="86"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BB17" s="8">
+        <f t="shared" si="86"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BC17" s="8">
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN17" s="9">
-        <f t="shared" si="72"/>
+      <c r="BD17" s="8">
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO17" s="9">
-        <f t="shared" si="72"/>
+      <c r="BE17" s="8">
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AP17" s="9">
-        <f t="shared" si="72"/>
+      <c r="BF17" s="8">
+        <f t="shared" si="86"/>
         <v>3.0000000000000027E-2</v>
       </c>
+      <c r="BG17" s="8">
+        <f t="shared" ref="BG17" si="87">BG3/BF3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BH17" s="8">
+        <f t="shared" ref="BH17" si="88">BH3/BG3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BI17" s="8">
+        <f t="shared" ref="BI17" si="89">BI3/BH3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BJ17" s="8">
+        <f t="shared" ref="BJ17" si="90">BJ3/BI3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BK17" s="8">
+        <f t="shared" ref="BK17" si="91">BK3/BJ3-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
     </row>
-    <row r="18" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:66" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <f>C5/C3</f>
         <v>0.58085673293707729</v>
       </c>
-      <c r="D18" s="9">
-        <f t="shared" ref="D18:V18" si="73">D5/D3</f>
+      <c r="D18" s="8">
+        <f t="shared" ref="D18:V18" si="92">D5/D3</f>
         <v>0.5569280343716434</v>
       </c>
-      <c r="E18" s="9">
-        <f t="shared" si="73"/>
+      <c r="E18" s="8">
+        <f t="shared" si="92"/>
         <v>0.59727134916624558</v>
       </c>
-      <c r="F18" s="9">
-        <f t="shared" si="73"/>
+      <c r="F18" s="8">
+        <f t="shared" si="92"/>
         <v>0.54820497973364213</v>
       </c>
-      <c r="G18" s="9">
-        <f t="shared" si="73"/>
+      <c r="G18" s="8">
+        <f t="shared" si="92"/>
         <v>0.58179206320703891</v>
       </c>
-      <c r="H18" s="9">
-        <f t="shared" si="73"/>
+      <c r="H18" s="8">
+        <f t="shared" si="92"/>
         <v>0.54768928220255653</v>
       </c>
-      <c r="I18" s="9">
-        <f t="shared" si="73"/>
+      <c r="I18" s="8">
+        <f t="shared" si="92"/>
         <v>0.59402320775711337</v>
       </c>
-      <c r="J18" s="9">
-        <f t="shared" si="73"/>
+      <c r="J18" s="8">
+        <f t="shared" si="92"/>
         <v>0.53451783534517838</v>
       </c>
-      <c r="K18" s="9">
-        <f t="shared" si="73"/>
+      <c r="K18" s="8">
+        <f t="shared" si="92"/>
         <v>0.58860983374602049</v>
       </c>
-      <c r="L18" s="9">
-        <f t="shared" si="73"/>
+      <c r="L18" s="8">
+        <f t="shared" si="92"/>
         <v>0.54770872567482742</v>
       </c>
-      <c r="M18" s="9">
-        <f t="shared" si="73"/>
+      <c r="M18" s="8">
+        <f t="shared" si="92"/>
         <v>0.60480349344978168</v>
       </c>
-      <c r="N18" s="9">
-        <f t="shared" si="73"/>
+      <c r="N18" s="8">
+        <f t="shared" si="92"/>
         <v>0.5347690710949663</v>
       </c>
-      <c r="O18" s="9">
-        <f t="shared" si="73"/>
+      <c r="O18" s="8">
+        <f t="shared" si="92"/>
         <v>0.59473595410831792</v>
       </c>
-      <c r="P18" s="9">
-        <f t="shared" si="73"/>
+      <c r="P18" s="8">
+        <f t="shared" si="92"/>
         <v>0.54533584796170032</v>
       </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="73"/>
+      <c r="Q18" s="8">
+        <f t="shared" si="92"/>
         <v>0.60771428571428576</v>
       </c>
-      <c r="R18" s="9">
-        <f t="shared" si="73"/>
+      <c r="R18" s="8">
+        <f t="shared" si="92"/>
         <v>0.50425230333097093</v>
       </c>
-      <c r="S18" s="9">
-        <f t="shared" si="73"/>
+      <c r="S18" s="8">
+        <f t="shared" si="92"/>
         <v>0.58401453224341504</v>
       </c>
-      <c r="T18" s="9">
-        <f t="shared" si="73"/>
+      <c r="T18" s="8">
+        <f t="shared" si="92"/>
         <v>0.54608879492600426</v>
       </c>
-      <c r="U18" s="9">
-        <f t="shared" si="73"/>
+      <c r="U18" s="8">
+        <f t="shared" si="92"/>
         <v>0.60475875743555851</v>
       </c>
-      <c r="V18" s="9">
-        <f t="shared" si="73"/>
+      <c r="V18" s="8">
+        <f t="shared" si="92"/>
         <v>0.53</v>
       </c>
-      <c r="W18" s="9">
-        <f t="shared" ref="W18:Z18" si="74">W5/W3</f>
+      <c r="W18" s="8">
+        <f t="shared" ref="W18:Z18" si="93">W5/W3</f>
         <v>0.59</v>
       </c>
-      <c r="X18" s="9">
-        <f t="shared" si="74"/>
+      <c r="X18" s="8">
+        <f t="shared" si="93"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="Y18" s="9">
-        <f t="shared" si="74"/>
+      <c r="Y18" s="8">
+        <f t="shared" si="93"/>
         <v>0.59</v>
       </c>
-      <c r="Z18" s="9">
-        <f t="shared" si="74"/>
+      <c r="Z18" s="8">
+        <f t="shared" si="93"/>
         <v>0.53</v>
       </c>
-      <c r="AB18" s="9">
-        <f t="shared" ref="AB18:AP18" si="75">AB5/AB3</f>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="8"/>
+      <c r="AD18" s="8"/>
+      <c r="AE18" s="8"/>
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="8"/>
+      <c r="AI18" s="8">
+        <f t="shared" ref="AI18:AJ18" si="94">AI5/AI3</f>
+        <v>0.60613496932515343</v>
+      </c>
+      <c r="AJ18" s="8">
+        <f t="shared" si="94"/>
+        <v>0.56490166414523446</v>
+      </c>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8">
+        <f t="shared" ref="AM18:AN18" si="95">AM5/AM3</f>
+        <v>0.60575296108291032</v>
+      </c>
+      <c r="AN18" s="8">
+        <f t="shared" si="95"/>
+        <v>0.56441535257363884</v>
+      </c>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="AR18" s="8">
+        <f t="shared" ref="AR18:BF18" si="96">AR5/AR3</f>
         <v>0.56962676962676961</v>
       </c>
-      <c r="AC18" s="9">
-        <f t="shared" si="75"/>
+      <c r="AS18" s="8">
+        <f t="shared" si="96"/>
         <v>0.56285770672982038</v>
       </c>
-      <c r="AD18" s="9">
-        <f t="shared" si="75"/>
+      <c r="AT18" s="8">
+        <f t="shared" si="96"/>
         <v>0.56674061041841961</v>
       </c>
-      <c r="AE18" s="9">
-        <f t="shared" si="75"/>
+      <c r="AU18" s="8">
+        <f t="shared" si="96"/>
         <v>0.55882768860920595</v>
       </c>
-      <c r="AF18" s="9">
-        <f t="shared" si="75"/>
+      <c r="AV18" s="8">
+        <f t="shared" si="96"/>
         <v>0.55822958533477107</v>
       </c>
-      <c r="AG18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56318245870447015</v>
-      </c>
-      <c r="AH18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AI18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AJ18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="AK18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AL18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AM18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AN18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AO18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="AP18" s="9">
-        <f t="shared" si="75"/>
-        <v>0.56999999999999995</v>
+      <c r="AW18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57057295425025256</v>
+      </c>
+      <c r="AX18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.56980564340323625</v>
+      </c>
+      <c r="AY18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57754471861351431</v>
+      </c>
+      <c r="AZ18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57838061710499067</v>
+      </c>
+      <c r="BA18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BB18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BC18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BD18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BE18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BF18" s="8">
+        <f t="shared" si="96"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BG18" s="8">
+        <f t="shared" ref="BG18:BK18" si="97">BG5/BG3</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BH18" s="8">
+        <f t="shared" si="97"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BI18" s="8">
+        <f t="shared" si="97"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BJ18" s="8">
+        <f t="shared" si="97"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BK18" s="8">
+        <f t="shared" si="97"/>
+        <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+    <row r="19" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <f>C9/C3</f>
         <v>0.14449682311949169</v>
       </c>
-      <c r="D19" s="9">
-        <f t="shared" ref="D19:V19" si="76">D9/D3</f>
+      <c r="D19" s="8">
+        <f t="shared" ref="D19:V19" si="98">D9/D3</f>
         <v>0.1611170784103115</v>
       </c>
-      <c r="E19" s="9">
-        <f t="shared" si="76"/>
+      <c r="E19" s="8">
+        <f t="shared" si="98"/>
         <v>0.20498568300488462</v>
       </c>
-      <c r="F19" s="9">
-        <f t="shared" si="76"/>
+      <c r="F19" s="8">
+        <f t="shared" si="98"/>
         <v>0.17356687898089171</v>
       </c>
-      <c r="G19" s="9">
-        <f t="shared" si="76"/>
+      <c r="G19" s="8">
+        <f t="shared" si="98"/>
         <v>0.1497575866403304</v>
       </c>
-      <c r="H19" s="9">
-        <f t="shared" si="76"/>
+      <c r="H19" s="8">
+        <f t="shared" si="98"/>
         <v>0.14913143231727302</v>
       </c>
-      <c r="I19" s="9">
-        <f t="shared" si="76"/>
+      <c r="I19" s="8">
+        <f t="shared" si="98"/>
         <v>0.19869655062788111</v>
       </c>
-      <c r="J19" s="9">
-        <f t="shared" si="76"/>
+      <c r="J19" s="8">
+        <f t="shared" si="98"/>
         <v>0.17916723179167232</v>
       </c>
-      <c r="K19" s="9">
-        <f t="shared" si="76"/>
+      <c r="K19" s="8">
+        <f t="shared" si="98"/>
         <v>0.15068977714892112</v>
       </c>
-      <c r="L19" s="9">
-        <f t="shared" si="76"/>
+      <c r="L19" s="8">
+        <f t="shared" si="98"/>
         <v>0.14642184557438795</v>
       </c>
-      <c r="M19" s="9">
-        <f t="shared" si="76"/>
+      <c r="M19" s="8">
+        <f t="shared" si="98"/>
         <v>0.20071740486587647</v>
       </c>
-      <c r="N19" s="9">
-        <f t="shared" si="76"/>
+      <c r="N19" s="8">
+        <f t="shared" si="98"/>
         <v>0.16696938245978205</v>
       </c>
-      <c r="O19" s="9">
-        <f t="shared" si="76"/>
+      <c r="O19" s="8">
+        <f t="shared" si="98"/>
         <v>0.16517631179348743</v>
       </c>
-      <c r="P19" s="9">
-        <f t="shared" si="76"/>
+      <c r="P19" s="8">
+        <f t="shared" si="98"/>
         <v>0.15377919628608733</v>
       </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="76"/>
+      <c r="Q19" s="8">
+        <f t="shared" si="98"/>
         <v>0.21542857142857144</v>
       </c>
-      <c r="R19" s="9">
-        <f t="shared" si="76"/>
+      <c r="R19" s="8">
+        <f t="shared" si="98"/>
         <v>0.14457831325301204</v>
       </c>
-      <c r="S19" s="9">
-        <f t="shared" si="76"/>
+      <c r="S19" s="8">
+        <f t="shared" si="98"/>
         <v>-0.15531335149863759</v>
       </c>
-      <c r="T19" s="9">
-        <f t="shared" si="76"/>
+      <c r="T19" s="8">
+        <f t="shared" si="98"/>
         <v>6.6596194503171252E-2</v>
       </c>
-      <c r="U19" s="9">
-        <f t="shared" si="76"/>
+      <c r="U19" s="8">
+        <f t="shared" si="98"/>
         <v>0.20125578321216128</v>
       </c>
-      <c r="V19" s="9">
-        <f t="shared" si="76"/>
+      <c r="V19" s="8">
+        <f t="shared" si="98"/>
         <v>9.7674529048599051E-2</v>
       </c>
-      <c r="W19" s="9">
-        <f t="shared" ref="W19:Z19" si="77">W9/W3</f>
+      <c r="W19" s="8">
+        <f t="shared" ref="W19:Z19" si="99">W9/W3</f>
         <v>0.10352143212914945</v>
       </c>
-      <c r="X19" s="9">
-        <f t="shared" si="77"/>
+      <c r="X19" s="8">
+        <f t="shared" si="99"/>
         <v>0.1335420393559929</v>
       </c>
-      <c r="Y19" s="9">
-        <f t="shared" si="77"/>
+      <c r="Y19" s="8">
+        <f t="shared" si="99"/>
         <v>0.19412786156342002</v>
       </c>
-      <c r="Z19" s="9">
-        <f t="shared" si="77"/>
+      <c r="Z19" s="8">
+        <f t="shared" si="99"/>
         <v>8.3955878694678798E-2</v>
       </c>
-      <c r="AB19" s="9">
-        <f t="shared" ref="AB19:AP19" si="78">AB9/AB3</f>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8"/>
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="8">
+        <f t="shared" ref="AI19:AJ19" si="100">AI9/AI3</f>
+        <v>0.2007361963190184</v>
+      </c>
+      <c r="AJ19" s="8">
+        <f t="shared" si="100"/>
+        <v>0.19213313161875945</v>
+      </c>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8">
+        <f t="shared" ref="AM19:AN19" si="101">AM9/AM3</f>
+        <v>0.1984529852550157</v>
+      </c>
+      <c r="AN19" s="8">
+        <f t="shared" si="101"/>
+        <v>0.19141128632351484</v>
+      </c>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AR19" s="8">
+        <f t="shared" ref="AR19:BF19" si="102">AR9/AR3</f>
         <v>0.17250107250107249</v>
       </c>
-      <c r="AC19" s="9">
-        <f t="shared" si="78"/>
+      <c r="AS19" s="8">
+        <f t="shared" si="102"/>
         <v>0.17031774225379909</v>
       </c>
-      <c r="AD19" s="9">
-        <f t="shared" si="78"/>
+      <c r="AT19" s="8">
+        <f t="shared" si="102"/>
         <v>0.1667176623575308</v>
       </c>
-      <c r="AE19" s="9">
-        <f t="shared" si="78"/>
+      <c r="AU19" s="8">
+        <f t="shared" si="102"/>
         <v>0.16867001343420773</v>
       </c>
-      <c r="AF19" s="9">
-        <f t="shared" si="78"/>
+      <c r="AV19" s="8">
+        <f t="shared" si="102"/>
         <v>7.3816292520341137E-2</v>
       </c>
-      <c r="AG19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.12949469798875168</v>
-      </c>
-      <c r="AH19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.15621440349450835</v>
-      </c>
-      <c r="AI19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.17327551160727503</v>
-      </c>
-      <c r="AJ19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.17873532157987113</v>
-      </c>
-      <c r="AK19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.18408997852158054</v>
-      </c>
-      <c r="AL19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.19045538786394298</v>
-      </c>
-      <c r="AM19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.19308391787805398</v>
-      </c>
-      <c r="AN19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.19568650885483305</v>
-      </c>
-      <c r="AO19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.19826342484304449</v>
-      </c>
-      <c r="AP19" s="9">
-        <f t="shared" si="78"/>
-        <v>0.20081492697214037</v>
-      </c>
-      <c r="AR19" t="s">
+      <c r="AW19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.15449559821041997</v>
+      </c>
+      <c r="AX19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.16942491326107648</v>
+      </c>
+      <c r="AY19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.18938993518235181</v>
+      </c>
+      <c r="AZ19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.1955632636156554</v>
+      </c>
+      <c r="BA19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.19046668615675708</v>
+      </c>
+      <c r="BB19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.18661638314874668</v>
+      </c>
+      <c r="BC19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.1895743192157508</v>
+      </c>
+      <c r="BD19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.1925026066509915</v>
+      </c>
+      <c r="BE19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.19540151523136209</v>
+      </c>
+      <c r="BF19" s="8">
+        <f t="shared" si="102"/>
+        <v>0.19827131176361334</v>
+      </c>
+      <c r="BG19" s="8">
+        <f t="shared" ref="BG19:BK19" si="103">BG9/BG3</f>
+        <v>0.19739767442114342</v>
+      </c>
+      <c r="BH19" s="8">
+        <f t="shared" si="103"/>
+        <v>0.19651444696502737</v>
+      </c>
+      <c r="BI19" s="8">
+        <f t="shared" si="103"/>
+        <v>0.19562150522625904</v>
+      </c>
+      <c r="BJ19" s="8">
+        <f t="shared" si="103"/>
+        <v>0.19471872293177489</v>
+      </c>
+      <c r="BK19" s="8">
+        <f t="shared" si="103"/>
+        <v>0.19380597165774591</v>
+      </c>
+      <c r="BM19" t="s">
         <v>47</v>
       </c>
-      <c r="AS19" s="9">
+      <c r="BN19" s="8">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="20" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
+    <row r="20" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="9">
-        <f t="shared" ref="G20:V20" si="79">G6/C6-1</f>
+      <c r="G20" s="8">
+        <f t="shared" ref="G20:V20" si="104">G6/C6-1</f>
         <v>0.13265849760255732</v>
       </c>
-      <c r="H20" s="9">
-        <f t="shared" si="79"/>
+      <c r="H20" s="8">
+        <f t="shared" si="104"/>
         <v>9.9846390168970789E-2</v>
       </c>
-      <c r="I20" s="9">
-        <f t="shared" si="79"/>
+      <c r="I20" s="8">
+        <f t="shared" si="104"/>
         <v>7.4670571010248876E-2</v>
       </c>
-      <c r="J20" s="9">
-        <f t="shared" si="79"/>
+      <c r="J20" s="8">
+        <f t="shared" si="104"/>
         <v>7.4912891986062657E-2</v>
       </c>
-      <c r="K20" s="9">
-        <f t="shared" si="79"/>
+      <c r="K20" s="8">
+        <f t="shared" si="104"/>
         <v>3.1984948259642598E-2</v>
       </c>
-      <c r="L20" s="9">
-        <f t="shared" si="79"/>
+      <c r="L20" s="8">
+        <f t="shared" si="104"/>
         <v>5.4469273743016799E-2</v>
       </c>
-      <c r="M20" s="9">
-        <f t="shared" si="79"/>
+      <c r="M20" s="8">
+        <f t="shared" si="104"/>
         <v>3.5422343324250649E-2</v>
       </c>
-      <c r="N20" s="9">
-        <f t="shared" si="79"/>
+      <c r="N20" s="8">
+        <f t="shared" si="104"/>
         <v>4.902755267423009E-2</v>
       </c>
-      <c r="O20" s="9">
-        <f t="shared" si="79"/>
+      <c r="O20" s="8">
+        <f t="shared" si="104"/>
         <v>-0.16043755697356432</v>
       </c>
-      <c r="P20" s="9">
-        <f t="shared" si="79"/>
+      <c r="P20" s="8">
+        <f t="shared" si="104"/>
         <v>-0.12538631346578366</v>
       </c>
-      <c r="Q20" s="9">
-        <f t="shared" si="79"/>
+      <c r="Q20" s="8">
+        <f t="shared" si="104"/>
         <v>-0.12807017543859645</v>
       </c>
-      <c r="R20" s="9">
-        <f t="shared" si="79"/>
+      <c r="R20" s="8">
+        <f t="shared" si="104"/>
         <v>-8.65198918501352E-2</v>
       </c>
-      <c r="S20" s="9">
-        <f t="shared" si="79"/>
+      <c r="S20" s="8">
+        <f t="shared" si="104"/>
         <v>-0.21389793702497284</v>
       </c>
-      <c r="T20" s="9">
-        <f t="shared" si="79"/>
+      <c r="T20" s="8">
+        <f t="shared" si="104"/>
         <v>-0.20646138313982842</v>
       </c>
-      <c r="U20" s="9">
-        <f t="shared" si="79"/>
+      <c r="U20" s="8">
+        <f t="shared" si="104"/>
         <v>-0.2716297786720322</v>
       </c>
-      <c r="V20" s="9">
-        <f t="shared" si="79"/>
+      <c r="V20" s="8">
+        <f t="shared" si="104"/>
         <v>-1.0993657505285359E-2</v>
       </c>
-      <c r="W20" s="9">
-        <f t="shared" ref="W20" si="80">W6/S6-1</f>
+      <c r="W20" s="8">
+        <f t="shared" ref="W20" si="105">W6/S6-1</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="X20" s="9">
-        <f t="shared" ref="X20" si="81">X6/T6-1</f>
+      <c r="X20" s="8">
+        <f t="shared" ref="X20" si="106">X6/T6-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="Y20" s="9">
-        <f t="shared" ref="Y20" si="82">Y6/U6-1</f>
+      <c r="Y20" s="8">
+        <f t="shared" ref="Y20" si="107">Y6/U6-1</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="Z20" s="9">
-        <f t="shared" ref="Z20" si="83">Z6/V6-1</f>
+      <c r="Z20" s="8">
+        <f t="shared" ref="Z20" si="108">Z6/V6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC20" s="9">
-        <f t="shared" ref="AC20:AP20" si="84">AC6/AB6-1</f>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8"/>
+      <c r="AD20" s="8"/>
+      <c r="AE20" s="8"/>
+      <c r="AF20" s="8"/>
+      <c r="AG20" s="8"/>
+      <c r="AH20" s="8"/>
+      <c r="AI20" s="8"/>
+      <c r="AJ20" s="8"/>
+      <c r="AK20" s="8"/>
+      <c r="AL20" s="8"/>
+      <c r="AM20" s="8">
+        <f t="shared" ref="AM20:AN20" si="109">AM6/AI6-1</f>
+        <v>2.3110066588327483E-2</v>
+      </c>
+      <c r="AN20" s="8">
+        <f t="shared" si="109"/>
+        <v>1.9903912148249825E-2</v>
+      </c>
+      <c r="AO20" s="8"/>
+      <c r="AP20" s="8"/>
+      <c r="AS20" s="8">
+        <f t="shared" ref="AS20:BF20" si="110">AS6/AR6-1</f>
         <v>9.4067278287461864E-2</v>
       </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="84"/>
+      <c r="AT20" s="8">
+        <f t="shared" si="110"/>
         <v>4.29338103756709E-2</v>
       </c>
-      <c r="AE20" s="9">
-        <f t="shared" si="84"/>
+      <c r="AU20" s="8">
+        <f t="shared" si="110"/>
         <v>-0.12349914236706694</v>
       </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="84"/>
+      <c r="AV20" s="8">
+        <f t="shared" si="110"/>
         <v>-0.16744129158512722</v>
       </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="84"/>
-        <v>0.147874247098575</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="84"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AI20" s="9">
-        <f t="shared" si="84"/>
+      <c r="AW20" s="8">
+        <f t="shared" si="110"/>
+        <v>0.26281768767445279</v>
+      </c>
+      <c r="AX20" s="8">
+        <f t="shared" si="110"/>
+        <v>0.14785946952070739</v>
+      </c>
+      <c r="AY20" s="8">
+        <f t="shared" si="110"/>
+        <v>9.9929056450795528E-2</v>
+      </c>
+      <c r="AZ20" s="8">
+        <f t="shared" si="110"/>
+        <v>6.4682576246199108E-2</v>
+      </c>
+      <c r="BA20" s="8">
+        <f t="shared" si="110"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BB20" s="8">
+        <f t="shared" si="110"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AJ20" s="9">
-        <f t="shared" si="84"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="84"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="84"/>
+      <c r="BC20" s="8">
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="84"/>
+      <c r="BD20" s="8">
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AN20" s="9">
-        <f t="shared" si="84"/>
+      <c r="BE20" s="8">
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO20" s="9">
-        <f t="shared" si="84"/>
+      <c r="BF20" s="8">
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AP20" s="9">
-        <f t="shared" si="84"/>
+      <c r="BG20" s="8">
+        <f t="shared" ref="BG20" si="111">BG6/BF6-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AR20" t="s">
+      <c r="BH20" s="8">
+        <f t="shared" ref="BH20" si="112">BH6/BG6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BI20" s="8">
+        <f t="shared" ref="BI20" si="113">BI6/BH6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BJ20" s="8">
+        <f t="shared" ref="BJ20" si="114">BJ6/BI6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BK20" s="8">
+        <f t="shared" ref="BK20" si="115">BK6/BJ6-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BM20" t="s">
         <v>48</v>
       </c>
-      <c r="AS20" s="9">
+      <c r="BN20" s="8">
         <v>0.06</v>
       </c>
     </row>
-    <row r="21" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
+    <row r="21" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <f>C12/C11</f>
         <v>0.2267037552155772</v>
       </c>
-      <c r="D21" s="9">
-        <f t="shared" ref="D21:AP21" si="85">D12/D11</f>
+      <c r="D21" s="8">
+        <f t="shared" ref="D21:BF21" si="116">D12/D11</f>
         <v>0.22772277227722773</v>
       </c>
-      <c r="E21" s="9">
-        <f t="shared" si="85"/>
+      <c r="E21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22745735174654752</v>
       </c>
-      <c r="F21" s="9">
-        <f t="shared" si="85"/>
+      <c r="F21" s="8">
+        <f t="shared" si="116"/>
         <v>0.21885245901639344</v>
       </c>
-      <c r="G21" s="9">
-        <f t="shared" si="85"/>
+      <c r="G21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22538552787663108</v>
       </c>
-      <c r="H21" s="9">
-        <f t="shared" si="85"/>
+      <c r="H21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22524483133841131</v>
       </c>
-      <c r="I21" s="9">
-        <f t="shared" si="85"/>
+      <c r="I21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22503961965134706</v>
       </c>
-      <c r="J21" s="9">
-        <f t="shared" si="85"/>
+      <c r="J21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22515060240963855</v>
       </c>
-      <c r="K21" s="9">
-        <f t="shared" si="85"/>
+      <c r="K21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22722029988465975</v>
       </c>
-      <c r="L21" s="9">
-        <f t="shared" si="85"/>
+      <c r="L21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22546972860125261</v>
       </c>
-      <c r="M21" s="9">
-        <f t="shared" si="85"/>
+      <c r="M21" s="8">
+        <f t="shared" si="116"/>
         <v>0.20061967467079783</v>
       </c>
-      <c r="N21" s="9">
-        <f t="shared" si="85"/>
+      <c r="N21" s="8">
+        <f t="shared" si="116"/>
         <v>0.23422053231939163</v>
       </c>
-      <c r="O21" s="9">
-        <f t="shared" si="85"/>
+      <c r="O21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22689075630252101</v>
       </c>
-      <c r="P21" s="9">
-        <f t="shared" si="85"/>
+      <c r="P21" s="8">
+        <f t="shared" si="116"/>
         <v>0.21083172147001933</v>
       </c>
-      <c r="Q21" s="9">
-        <f t="shared" si="85"/>
+      <c r="Q21" s="8">
+        <f t="shared" si="116"/>
         <v>0.20995962314939434</v>
       </c>
-      <c r="R21" s="9">
-        <f t="shared" si="85"/>
+      <c r="R21" s="8">
+        <f t="shared" si="116"/>
         <v>0.23758278145695363</v>
       </c>
-      <c r="S21" s="9">
-        <f t="shared" si="85"/>
+      <c r="S21" s="8">
+        <f t="shared" si="116"/>
         <v>0.23897058823529413</v>
       </c>
-      <c r="T21" s="9">
-        <f t="shared" si="85"/>
+      <c r="T21" s="8">
+        <f t="shared" si="116"/>
         <v>0.23131672597864769</v>
       </c>
-      <c r="U21" s="9">
-        <f t="shared" si="85"/>
+      <c r="U21" s="8">
+        <f t="shared" si="116"/>
         <v>-0.10951979780960404</v>
       </c>
-      <c r="V21" s="9">
-        <f t="shared" si="85"/>
+      <c r="V21" s="8">
+        <f t="shared" si="116"/>
         <v>0.8072354656430698</v>
       </c>
-      <c r="W21" s="9">
-        <f t="shared" ref="W21:Z21" si="86">W12/W11</f>
+      <c r="W21" s="8">
+        <f t="shared" ref="W21:Z21" si="117">W12/W11</f>
         <v>0.22</v>
       </c>
-      <c r="X21" s="9">
-        <f t="shared" si="86"/>
+      <c r="X21" s="8">
+        <f t="shared" si="117"/>
         <v>0.22000000000000003</v>
       </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="86"/>
+      <c r="Y21" s="8">
+        <f t="shared" si="117"/>
         <v>0.22000000000000003</v>
       </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="86"/>
+      <c r="Z21" s="8">
+        <f t="shared" si="117"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="85"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
+      <c r="AE21" s="8"/>
+      <c r="AF21" s="8"/>
+      <c r="AG21" s="8"/>
+      <c r="AH21" s="8"/>
+      <c r="AI21" s="8">
+        <f t="shared" ref="AI21:AJ21" si="118">AI12/AI11</f>
+        <v>0.2232196289646918</v>
+      </c>
+      <c r="AJ21" s="8">
+        <f t="shared" si="118"/>
+        <v>0.23196678775298391</v>
+      </c>
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="8">
+        <f t="shared" ref="AM21:AN21" si="119">AM12/AM11</f>
+        <v>0.21889952153110048</v>
+      </c>
+      <c r="AN21" s="8">
+        <f t="shared" si="119"/>
+        <v>0.23005181347150258</v>
+      </c>
+      <c r="AO21" s="8"/>
+      <c r="AP21" s="8"/>
+      <c r="AR21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22481000245158128</v>
       </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="85"/>
+      <c r="AS21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22518382352941177</v>
       </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="85"/>
+      <c r="AT21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22116903633491311</v>
       </c>
-      <c r="AE21" s="9">
-        <f t="shared" si="85"/>
+      <c r="AU21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22072649572649572</v>
       </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="85"/>
+      <c r="AV21" s="8">
+        <f t="shared" si="116"/>
         <v>0.21071428571428572</v>
       </c>
-      <c r="AG21" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21999999999999992</v>
-      </c>
-      <c r="AH21" s="9">
-        <f t="shared" si="85"/>
+      <c r="AW21" s="8">
+        <f t="shared" si="116"/>
+        <v>0.22606002858504048</v>
+      </c>
+      <c r="AX21" s="8">
+        <f t="shared" si="116"/>
+        <v>0.22605936158297554</v>
+      </c>
+      <c r="AY21" s="8">
+        <f t="shared" si="116"/>
+        <v>0.21473285776677828</v>
+      </c>
+      <c r="AZ21" s="8">
+        <f t="shared" si="116"/>
+        <v>0.22436320443447275</v>
+      </c>
+      <c r="BA21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22</v>
       </c>
-      <c r="AI21" s="9">
-        <f t="shared" si="85"/>
+      <c r="BB21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22</v>
       </c>
-      <c r="AJ21" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="AK21" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="AL21" s="9">
-        <f t="shared" si="85"/>
+      <c r="BC21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22</v>
       </c>
-      <c r="AM21" s="9">
-        <f t="shared" si="85"/>
+      <c r="BD21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22</v>
       </c>
-      <c r="AN21" s="9">
-        <f t="shared" si="85"/>
+      <c r="BE21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22</v>
       </c>
-      <c r="AO21" s="9">
-        <f t="shared" si="85"/>
+      <c r="BF21" s="8">
+        <f t="shared" si="116"/>
         <v>0.22</v>
       </c>
-      <c r="AP21" s="9">
-        <f t="shared" si="85"/>
+      <c r="BG21" s="8">
+        <f t="shared" ref="BG21:BK21" si="120">BG12/BG11</f>
         <v>0.22</v>
       </c>
-      <c r="AR21" t="s">
+      <c r="BH21" s="8">
+        <f t="shared" si="120"/>
+        <v>0.22</v>
+      </c>
+      <c r="BI21" s="8">
+        <f t="shared" si="120"/>
+        <v>0.22</v>
+      </c>
+      <c r="BJ21" s="8">
+        <f t="shared" si="120"/>
+        <v>0.22</v>
+      </c>
+      <c r="BK21" s="8">
+        <f t="shared" si="120"/>
+        <v>0.22</v>
+      </c>
+      <c r="BM21" t="s">
         <v>49</v>
       </c>
-      <c r="AS21" s="5">
-        <f>NPV(AS20,AF13:EM13)</f>
-        <v>76192.091631891119</v>
+      <c r="BN21" s="5">
+        <f>NPV(BN20,BA13:FH13)</f>
+        <v>108065.51873260055</v>
       </c>
     </row>
-    <row r="22" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR22" t="s">
+    <row r="22" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="8">
+        <f>C13/C3</f>
+        <v>0.11395777823324452</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" ref="D22:Z22" si="121">D13/D3</f>
+        <v>0.12567132116004295</v>
+      </c>
+      <c r="E22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.16018191005558363</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.13795599305153444</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.11725623989944335</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.11668305473615208</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.15546018121125418</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.13956327139563271</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.11850017686593563</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.11644695543000627</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.16094822208359327</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.13064348728593669</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.12417749282942467</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.11838096619759177</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.1677142857142857</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.10878809355067329</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" si="121"/>
+        <v>-0.12534059945504086</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" si="121"/>
+        <v>4.5665961945031711E-2</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.21761401189689358</v>
+      </c>
+      <c r="V22" s="8">
+        <f t="shared" si="121"/>
+        <v>1.8523033085325349E-2</v>
+      </c>
+      <c r="W22" s="8">
+        <f t="shared" si="121"/>
+        <v>7.6176092115671959E-2</v>
+      </c>
+      <c r="X22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.10035729386892181</v>
+      </c>
+      <c r="Y22" s="8">
+        <f t="shared" si="121"/>
+        <v>0.14790474073183918</v>
+      </c>
+      <c r="Z22" s="8">
+        <f t="shared" si="121"/>
+        <v>6.4383118116646723E-2</v>
+      </c>
+      <c r="AI22" s="8">
+        <f t="shared" ref="AI22:AJ22" si="122">AI13/AI3</f>
+        <v>0.15926380368098159</v>
+      </c>
+      <c r="AJ22" s="8">
+        <f t="shared" si="122"/>
+        <v>0.14926878466969237</v>
+      </c>
+      <c r="AM22" s="8">
+        <f t="shared" ref="AM22:AN22" si="123">AM13/AM3</f>
+        <v>0.15784384819917816</v>
+      </c>
+      <c r="AN22" s="8">
+        <f t="shared" si="123"/>
+        <v>0.14737677278587721</v>
+      </c>
+      <c r="AR22" s="8">
+        <f t="shared" ref="AR22:BK22" si="124">AR13/AR3</f>
+        <v>0.13564993564993566</v>
+      </c>
+      <c r="AS22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.13309650680876259</v>
+      </c>
+      <c r="AT22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.13198959687906373</v>
+      </c>
+      <c r="AU22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.12893304108039313</v>
+      </c>
+      <c r="AV22" s="8">
+        <f t="shared" si="124"/>
+        <v>5.4161356729732379E-2</v>
+      </c>
+      <c r="AW22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.11722470775003609</v>
+      </c>
+      <c r="AX22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.12729896527372656</v>
+      </c>
+      <c r="AY22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15005424652961305</v>
+      </c>
+      <c r="AZ22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15212776972458067</v>
+      </c>
+      <c r="BA22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.14891240057008509</v>
+      </c>
+      <c r="BB22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.14583402228175932</v>
+      </c>
+      <c r="BC22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.14676359483896745</v>
+      </c>
+      <c r="BD22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.14904061955695402</v>
+      </c>
+      <c r="BE22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15128452476148743</v>
+      </c>
+      <c r="BF22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15350597337645375</v>
+      </c>
+      <c r="BG22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.152796316840319</v>
+      </c>
+      <c r="BH22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.1521128262098248</v>
+      </c>
+      <c r="BI22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15142155834664223</v>
+      </c>
+      <c r="BJ22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15072267432295716</v>
+      </c>
+      <c r="BK22" s="8">
+        <f t="shared" si="124"/>
+        <v>0.15001607273645448</v>
+      </c>
+      <c r="BM22" t="s">
         <v>53</v>
       </c>
-      <c r="AS22" s="5">
+      <c r="BN22" s="5">
         <f>Main!D8</f>
-        <v>7821</v>
+        <v>10012</v>
       </c>
     </row>
-    <row r="23" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR23" t="s">
+    <row r="23" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="BM23" t="s">
         <v>50</v>
       </c>
-      <c r="AS23" s="5">
-        <f>AS21+AS22</f>
-        <v>84013.091631891119</v>
+      <c r="BN23" s="5">
+        <f>BN21+BN22</f>
+        <v>118077.51873260055</v>
       </c>
     </row>
-    <row r="24" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR24" t="s">
+    <row r="24" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="BM24" t="s">
         <v>51</v>
       </c>
-      <c r="AS24" s="4">
-        <f>AS23/AP14</f>
-        <v>26.970494905904051</v>
+      <c r="BN24" s="4">
+        <f>BN23/BF14</f>
+        <v>37.896372916297757</v>
       </c>
     </row>
-    <row r="25" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR25" t="s">
+    <row r="25" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="BM25" t="s">
         <v>52</v>
       </c>
-      <c r="AS25" s="4">
+      <c r="BN25" s="4">
         <f>Main!D3</f>
-        <v>31.81</v>
+        <v>46.89</v>
       </c>
     </row>
-    <row r="26" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR26" s="1" t="s">
+    <row r="26" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="BM26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AS26" s="12">
-        <f>AS24/AS25-1</f>
-        <v>-0.15213785269085034</v>
+      <c r="BN26" s="10">
+        <f>BN24/BN25-1</f>
+        <v>-0.19180266759868292</v>
       </c>
     </row>
-    <row r="27" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR27" t="s">
+    <row r="27" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="BM27" t="s">
         <v>55</v>
       </c>
-      <c r="AS27" s="6" t="s">
+      <c r="BN27" s="6" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="AJ28" s="9">
+        <v>18065</v>
+      </c>
+      <c r="AN28" s="9">
+        <f>18357</f>
+        <v>18357</v>
+      </c>
+    </row>
+    <row r="29" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="AJ29" s="12">
+        <v>7524</v>
+      </c>
+      <c r="AN29" s="12">
+        <v>7654</v>
+      </c>
+    </row>
+    <row r="30" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="AJ30" s="9">
+        <f t="shared" ref="AJ30" si="125">AJ28-AJ29</f>
+        <v>10541</v>
+      </c>
+      <c r="AN30" s="9">
+        <f t="shared" ref="AN30" si="126">AN28-AN29</f>
+        <v>10703</v>
+      </c>
+    </row>
+    <row r="31" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="AJ31" s="5">
+        <v>5467</v>
+      </c>
+      <c r="AN31" s="5">
+        <v>5584</v>
+      </c>
+    </row>
+    <row r="32" spans="2:66" x14ac:dyDescent="0.3">
+      <c r="AJ32" s="5">
+        <v>34</v>
+      </c>
+      <c r="AN32" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ33" s="5">
+        <v>1499</v>
+      </c>
+      <c r="AN33" s="5">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="34" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ34" s="9">
+        <f t="shared" ref="AJ34" si="127">AJ30-AJ31-AJ32-AJ33</f>
+        <v>3541</v>
+      </c>
+      <c r="AN34" s="9">
+        <f t="shared" ref="AN34" si="128">AN30-AN31-AN32-AN33</f>
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="35" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ35" s="5">
+        <f>-12-45</f>
+        <v>-57</v>
+      </c>
+      <c r="AN35" s="5">
+        <f>12-42</f>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="36" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ36" s="9">
+        <f t="shared" ref="AJ36" si="129">AJ34-AJ35</f>
+        <v>3598</v>
+      </c>
+      <c r="AN36" s="9">
+        <f t="shared" ref="AN36" si="130">AN34-AN35</f>
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="37" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ37" s="5">
+        <v>820</v>
+      </c>
+      <c r="AN37" s="5">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="38" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ38" s="9">
+        <f t="shared" ref="AJ38" si="131">AJ36-AJ37</f>
+        <v>2778</v>
+      </c>
+      <c r="AN38" s="9">
+        <f t="shared" ref="AN38" si="132">AN36-AN37</f>
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="39" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ39" s="5">
+        <v>3115</v>
+      </c>
+      <c r="AN39" s="5">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="40" spans="36:40" x14ac:dyDescent="0.3">
+      <c r="AJ40" s="7">
+        <f t="shared" ref="AJ40" si="133">AJ38/AJ39</f>
+        <v>0.89181380417335476</v>
+      </c>
+      <c r="AN40" s="7">
+        <f t="shared" ref="AN40" si="134">AN38/AN39</f>
+        <v>0.89630818619582664</v>
       </c>
     </row>
   </sheetData>
